--- a/data/smart_buildings_dataset.xlsx
+++ b/data/smart_buildings_dataset.xlsx
@@ -511,75 +511,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN18"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
-    <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
-    <col width="22" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="34" customWidth="1" min="33" max="33"/>
-    <col width="35" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="34" customWidth="1" min="31" max="31"/>
+    <col width="35" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="34" max="34"/>
+    <col width="33" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
-    <col width="33" customWidth="1" min="37" max="37"/>
-    <col width="28" customWidth="1" min="38" max="38"/>
-    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
+    <col width="24" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="24" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="24" customWidth="1" min="42" max="42"/>
-    <col width="28" customWidth="1" min="43" max="43"/>
-    <col width="25" customWidth="1" min="44" max="44"/>
-    <col width="25" customWidth="1" min="45" max="45"/>
-    <col width="28" customWidth="1" min="46" max="46"/>
-    <col width="28" customWidth="1" min="47" max="47"/>
-    <col width="35" customWidth="1" min="48" max="48"/>
-    <col width="11" customWidth="1" min="49" max="49"/>
-    <col width="31" customWidth="1" min="50" max="50"/>
+    <col width="28" customWidth="1" min="41" max="41"/>
+    <col width="25" customWidth="1" min="42" max="42"/>
+    <col width="25" customWidth="1" min="43" max="43"/>
+    <col width="28" customWidth="1" min="44" max="44"/>
+    <col width="28" customWidth="1" min="45" max="45"/>
+    <col width="35" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
+    <col width="31" customWidth="1" min="48" max="48"/>
+    <col width="30" customWidth="1" min="49" max="49"/>
+    <col width="28" customWidth="1" min="50" max="50"/>
     <col width="30" customWidth="1" min="51" max="51"/>
-    <col width="28" customWidth="1" min="52" max="52"/>
-    <col width="30" customWidth="1" min="53" max="53"/>
-    <col width="24" customWidth="1" min="54" max="54"/>
-    <col width="29" customWidth="1" min="55" max="55"/>
+    <col width="24" customWidth="1" min="52" max="52"/>
+    <col width="29" customWidth="1" min="53" max="53"/>
+    <col width="28" customWidth="1" min="54" max="54"/>
+    <col width="26" customWidth="1" min="55" max="55"/>
     <col width="28" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="28" customWidth="1" min="58" max="58"/>
-    <col width="22" customWidth="1" min="59" max="59"/>
-    <col width="17" customWidth="1" min="60" max="60"/>
-    <col width="60" customWidth="1" min="61" max="61"/>
-    <col width="46" customWidth="1" min="62" max="62"/>
-    <col width="18" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="57" max="57"/>
+    <col width="17" customWidth="1" min="58" max="58"/>
+    <col width="60" customWidth="1" min="59" max="59"/>
+    <col width="46" customWidth="1" min="60" max="60"/>
+    <col width="18" customWidth="1" min="61" max="61"/>
+    <col width="60" customWidth="1" min="62" max="62"/>
+    <col width="47" customWidth="1" min="63" max="63"/>
     <col width="60" customWidth="1" min="64" max="64"/>
     <col width="47" customWidth="1" min="65" max="65"/>
     <col width="60" customWidth="1" min="66" max="66"/>
+    <col width="60" customWidth="1" min="67" max="67"/>
+    <col width="60" customWidth="1" min="68" max="68"/>
+    <col width="30" customWidth="1" min="69" max="69"/>
+    <col width="45" customWidth="1" min="70" max="70"/>
+    <col width="30" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -605,310 +610,320 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>source_study</t>
+          <t>address</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>city</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>municipality</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>county</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>municipality</t>
+          <t>country</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>county</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>location_precision</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>location_precision</t>
+          <t>building_category</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>floor_area_category</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>building_category</t>
+          <t>floor_area_m2</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>floor_area_category</t>
+          <t>construction_period</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>floor_area_m2</t>
+          <t>construction_year</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>construction_period</t>
+          <t>latest_renovation_year</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>construction_year</t>
+          <t>reference_year</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>latest_renovation_year</t>
+          <t>reference_year_estimated</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>reference_year</t>
+          <t>assessed_state</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>reference_year_estimated</t>
+          <t>n_sri_domains_assessed</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>assessed_state</t>
+          <t>sri_domains_not_assessed</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>n_sri_domains_assessed</t>
+          <t>epc_label</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>sri_domains_not_assessed</t>
+          <t>sri_total_pct</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>epc_label</t>
+          <t>sri_class</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sri_total_pct</t>
+          <t>sri_kf1_building_pct</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sri_class</t>
+          <t>sri_kf2_user_pct</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>sri_kf1_building_pct</t>
+          <t>sri_kf3_grid_pct</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>sri_kf2_user_pct</t>
+          <t>sri_impact_energy_efficiency_pct</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>sri_kf3_grid_pct</t>
+          <t>sri_impact_energy_flexibility_pct</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_energy_efficiency_pct</t>
+          <t>sri_impact_comfort_pct</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_energy_flexibility_pct</t>
+          <t>sri_impact_convenience_pct</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_comfort_pct</t>
+          <t>sri_impact_health_wellbeing_pct</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_convenience_pct</t>
+          <t>sri_impact_maintenance_pct</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_health_wellbeing_pct</t>
+          <t>sri_impact_information_pct</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_maintenance_pct</t>
+          <t>sri_domain_heating_pct</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>sri_impact_information_pct</t>
+          <t>sri_domain_dhw_pct</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_heating_pct</t>
+          <t>sri_domain_cooling_pct</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_dhw_pct</t>
+          <t>sri_domain_ventilation_pct</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_cooling_pct</t>
+          <t>sri_domain_lighting_pct</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_ventilation_pct</t>
+          <t>sri_domain_envelope_pct</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_lighting_pct</t>
+          <t>sri_domain_electricity_pct</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_envelope_pct</t>
+          <t>sri_domain_ev_charging_pct</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_electricity_pct</t>
+          <t>sri_domain_monitoring_control_pct</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_ev_charging_pct</t>
+          <t>sbp_level</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>sri_domain_monitoring_control_pct</t>
+          <t>sbp_enabling_technology_level</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>sbp_level</t>
+          <t>sbp_indoor_environment_level</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>sbp_enabling_technology_level</t>
+          <t>sbp_energy_resources_level</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>sbp_indoor_environment_level</t>
+          <t>sbp_safety_reliability_level</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>sbp_energy_resources_level</t>
+          <t>sbp_adaptability_level</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>sbp_safety_reliability_level</t>
+          <t>sbp_enabling_technology_pct</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>sbp_adaptability_level</t>
+          <t>sbp_indoor_environment_pct</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>sbp_enabling_technology_pct</t>
+          <t>sbp_energy_resources_pct</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>sbp_indoor_environment_pct</t>
+          <t>sbp_safety_reliability_pct</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>sbp_energy_resources_pct</t>
+          <t>sbp_adaptability_pct</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>sbp_safety_reliability_pct</t>
+          <t>assessment_year</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>sbp_adaptability_pct</t>
+          <t>sri_method</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>assessment_year</t>
+          <t>sbp_tool</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>sri_method</t>
+          <t>detail_available</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>sbp_tool</t>
+          <t>main_reference</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>detail_available</t>
+          <t>main_reference_url</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>building_info_reference</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>reference_url</t>
+          <t>building_info_reference_url</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>performance_info_reference</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>performance_info_reference_url</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -937,17 +952,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Dronning Eufemias gate (Barcode), Bjørvika</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dronning Eufemias gate (Barcode), Bjørvika</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -957,196 +972,190 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="J2" t="n">
         <v>59.90759</v>
       </c>
-      <c r="M2" t="n">
+      <c r="K2" t="n">
         <v>10.76007</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Approximate (street)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Office building</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Approximate (street)</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Office building</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Office</t>
+          <t>&gt; 25 000 m²</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>&gt; 25 000 m²</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
           <t>2000–2010</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
+      <c r="T2" t="n">
         <v>2005</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Current state</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>8</v>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Current state</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
           <t>Domestic hot water</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Class 4 (50–65%)</t>
+        </is>
+      </c>
       <c r="AB2" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Class 4 (50–65%)</t>
-        </is>
+        <v>62.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>62.4</v>
+        <v>49.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>75.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="AF2" t="n">
         <v>49.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>65.5</v>
+        <v>83.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>49.5</v>
+        <v>72.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>83.2</v>
+        <v>86.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>72.8</v>
+        <v>59.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>86.2</v>
+        <v>61.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>61.5</v>
+        <v>55.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>81.3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>70.2</v>
+      </c>
       <c r="AP2" t="n">
-        <v>81.3</v>
+        <v>93.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>70.2</v>
+        <v>54</v>
       </c>
       <c r="AR2" t="n">
-        <v>93.3</v>
+        <v>55.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>54</v>
+        <v>-25</v>
       </c>
       <c r="AT2" t="n">
-        <v>55.6</v>
+        <v>73</v>
       </c>
       <c r="AU2" t="n">
-        <v>-25</v>
+        <v>0.97</v>
       </c>
       <c r="AV2" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.57</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.33</v>
+        <v>50</v>
       </c>
       <c r="BC2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BD2" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="BH2" t="n">
         <v>2026</v>
       </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
       <c r="BN2" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>Report Table 2 states 'After 2010 (C)' while Table 3 and Figure 9 use 2000–2010; 2000–2010 kept. Exact street number to verify.</t>
         </is>
@@ -1175,214 +1184,208 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Kjølnes ring 56</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kjølnes ring 56</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Telemark</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Telemark</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="J3" t="n">
         <v>59.13876</v>
       </c>
-      <c r="M3" t="n">
+      <c r="K3" t="n">
         <v>9.67216</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Address (campus)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>University educational building</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Address (campus)</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>University educational building</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Education</t>
+          <t>&gt; 25 000 m²</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>&gt; 25 000 m²</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
           <t>1960–1990</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
+      <c r="T3" t="n">
         <v>1975</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Original state</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="W3" t="n">
         <v>9</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>42.7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>42.7</v>
+        <v>16.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>48.5</v>
       </c>
       <c r="AF3" t="n">
         <v>16.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.2</v>
+        <v>36.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>47</v>
+        <v>41.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36.1</v>
+        <v>36.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>41.2</v>
+        <v>43.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>36.8</v>
+        <v>39.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>43.5</v>
+        <v>36.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.8</v>
+        <v>23.9</v>
       </c>
       <c r="AO3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>36.7</v>
       </c>
-      <c r="AP3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
       <c r="BC3" t="n">
-        <v>44.4</v>
+        <v>36.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>36.7</v>
+        <v>47.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>36.7</v>
+        <v>33.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="BH3" t="n">
         <v>2026</v>
       </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
       <c r="BN3" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>Campus address used; assessed building within campus not specified.</t>
         </is>
@@ -1411,216 +1414,210 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Osloveien 16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Røros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osloveien 16</t>
+          <t>Røros</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Røros</t>
+          <t>Trøndelag</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Røros</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Trøndelag</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="J4" t="n">
         <v>62.57029</v>
       </c>
-      <c r="M4" t="n">
+      <c r="K4" t="n">
         <v>11.38708</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Approximate (company address, to verify)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Office building</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Approximate (company address, to verify)</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Office building</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Office</t>
+          <t>1 000 – 10 000 m²</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 000 – 10 000 m²</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
           <t>1960–1990</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
+      <c r="T4" t="n">
         <v>1975</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Current state</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>8</v>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Current state</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
           <t>Domestic hot water</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Class 7 (&lt;20%)</t>
+        </is>
+      </c>
       <c r="AB4" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Class 7 (&lt;20%)</t>
-        </is>
+        <v>22.7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>20.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>22.7</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>20.7</v>
+        <v>30.9</v>
       </c>
       <c r="AF4" t="n">
         <v>1.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>30.9</v>
+        <v>37.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.1</v>
+        <v>19.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>37.4</v>
+        <v>19.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19.7</v>
+        <v>14.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>19.2</v>
+        <v>6.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>6.5</v>
+        <v>22.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>27.9</v>
+      </c>
       <c r="AP4" t="n">
-        <v>23.4</v>
+        <v>29.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27.9</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>29.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>-27.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>-27.8</v>
+        <v>-1.28</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.9</v>
+        <v>-2</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1.28</v>
+        <v>-1.8</v>
       </c>
       <c r="AX4" t="n">
         <v>-2</v>
       </c>
       <c r="AY4" t="n">
-        <v>-1.8</v>
+        <v>0.86</v>
       </c>
       <c r="AZ4" t="n">
         <v>-2</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-2</v>
+        <v>3.3</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.3</v>
+        <v>47.6</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
         <v>2026</v>
       </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
       <c r="BN4" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
         <is>
           <t>Address from public company directories, not from the report.</t>
         </is>
@@ -1649,17 +1646,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Nedre Skøyen vei 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nedre Skøyen vei 2</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1669,194 +1666,187 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="J5" t="n">
         <v>59.92313</v>
       </c>
-      <c r="M5" t="n">
+      <c r="K5" t="n">
         <v>10.68027</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Office building</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Office building</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Office</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
           <t>2000–2010</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="T5" t="n">
         <v>2005</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="W5" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB5" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>42.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>48.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>42.3</v>
+        <v>7.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>48.3</v>
+        <v>50.4</v>
       </c>
       <c r="AF5" t="n">
         <v>7.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>50.4</v>
+        <v>53.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>7.2</v>
+        <v>42.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>53.7</v>
+        <v>53.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42.9</v>
+        <v>34.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>53.1</v>
+        <v>43.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>34.1</v>
+        <v>26.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>43.4</v>
+        <v>61.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.4</v>
+        <v>43.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>61.1</v>
+        <v>57.6</v>
       </c>
       <c r="AP5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BC5" t="n">
         <v>43.3</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>27.8</v>
       </c>
-      <c r="AV5" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>43.3</v>
-      </c>
       <c r="BF5" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="BH5" t="n">
         <v>2026</v>
       </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1881,216 +1871,211 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Vestfjordgaten 4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Sandvika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vestfjordgaten 4</t>
+          <t>Bærum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sandvika</t>
+          <t>Akershus</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bærum</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Akershus</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="J6" t="n">
         <v>59.89046</v>
       </c>
-      <c r="M6" t="n">
+      <c r="K6" t="n">
         <v>10.52205</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Office building</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Office building</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Office</t>
+          <t>1 000 – 10 000 m²</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 000 – 10 000 m²</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
           <t>2000–2010</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
+      <c r="S6" t="n">
         <v>2020</v>
       </c>
-      <c r="V6" t="n">
+      <c r="T6" t="n">
         <v>2020</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Renovated (2020)</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="W6" t="n">
         <v>9</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB6" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>53.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>45.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>53.3</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>45.4</v>
+        <v>67.3</v>
       </c>
       <c r="AF6" t="n">
         <v>4</v>
       </c>
       <c r="AG6" t="n">
-        <v>67.3</v>
+        <v>54.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="AI6" t="n">
-        <v>54.3</v>
+        <v>49.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>41</v>
+        <v>39.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>49.1</v>
+        <v>37.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>39.3</v>
+        <v>43.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>37.1</v>
+        <v>68.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.5</v>
+        <v>32.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>68.3</v>
+        <v>76</v>
       </c>
       <c r="AP6" t="n">
-        <v>32.4</v>
+        <v>29.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>29.3</v>
+        <v>25</v>
       </c>
       <c r="AS6" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AW6" t="n">
         <v>0</v>
       </c>
-      <c r="AT6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="AX6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.33</v>
+        <v>33.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>24.1</v>
+        <v>33.3</v>
       </c>
       <c r="BD6" t="n">
         <v>33.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>33.3</v>
+        <v>27.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="BH6" t="n">
         <v>2026</v>
       </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
       <c r="BN6" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
         <is>
           <t>Constructed 2000–2010, latest renovation 2020 (report Table 2).</t>
         </is>
@@ -2119,214 +2104,208 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Vagleveien 75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Sandnes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Vagleveien 75</t>
+          <t>Sandnes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sandnes</t>
+          <t>Rogaland</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sandnes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Rogaland</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="J7" t="n">
         <v>58.81136</v>
       </c>
-      <c r="M7" t="n">
+      <c r="K7" t="n">
         <v>5.72227</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Approximate (locality Vagle)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Logistic distribution centre (cold storage)</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Approximate (locality Vagle)</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Logistic distribution centre (cold storage)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Logistics</t>
+          <t>&gt; 25 000 m²</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>&gt; 25 000 m²</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
           <t>After 2010</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
+      <c r="T7" t="n">
         <v>2018</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Original state</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="W7" t="n">
         <v>9</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Class 3 (65–80%)</t>
+        </is>
+      </c>
       <c r="AB7" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Class 3 (65–80%)</t>
-        </is>
+        <v>64.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>69.90000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>64.8</v>
+        <v>86.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>69.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="AF7" t="n">
         <v>86.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>79.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>86.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>74.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>68.5</v>
+        <v>70.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>77.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>70.5</v>
+        <v>57.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>77.5</v>
+        <v>89</v>
       </c>
       <c r="AO7" t="n">
-        <v>57.4</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AQ7" t="n">
-        <v>70</v>
+        <v>19.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>82</v>
+        <v>74.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>19.8</v>
+        <v>-25</v>
       </c>
       <c r="AT7" t="n">
-        <v>74.3</v>
+        <v>63</v>
       </c>
       <c r="AU7" t="n">
-        <v>-25</v>
+        <v>1.24</v>
       </c>
       <c r="AV7" t="n">
-        <v>63</v>
+        <v>1.67</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.24</v>
+        <v>0.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.4</v>
+        <v>0.86</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.86</v>
+        <v>61.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.33</v>
+        <v>40</v>
       </c>
       <c r="BC7" t="n">
-        <v>61.1</v>
+        <v>63.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>40</v>
+        <v>47.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>63.3</v>
+        <v>55.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="BH7" t="n">
         <v>2026</v>
       </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
       <c r="BN7" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
         <is>
           <t>Address not found in the Kartverket register; positioned at Vagle locality.</t>
         </is>
@@ -2355,220 +2334,216 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EDISON pilots (2026)</t>
+          <t>Høgskoleringen 7B</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Høgskoleringen 7B</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Trøndelag</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Trøndelag</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="J8" t="n">
         <v>63.4148</v>
       </c>
-      <c r="M8" t="n">
+      <c r="K8" t="n">
         <v>10.40877</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Office building / living lab</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Office / laboratory</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Office building / living lab</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Office / laboratory</t>
-        </is>
+          <t>1 000 – 10 000 m²</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1800</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 000 – 10 000 m²</t>
+          <t>After 2010</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>After 2010</t>
-        </is>
+        <v>2020</v>
       </c>
       <c r="T8" t="n">
         <v>2020</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>2020</v>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Original state</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>8</v>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Original state</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
           <t>Cooling</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Class 4 (50–65%)</t>
+        </is>
+      </c>
       <c r="AB8" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Class 4 (50–65%)</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>76.40000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>68</v>
+        <v>44.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>76.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AF8" t="n">
         <v>44.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>71.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>44.4</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>85.2</v>
+        <v>80.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70.90000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AK8" t="n">
-        <v>80.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AL8" t="n">
-        <v>64.90000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>51.9</v>
+        <v>48.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>90.40000000000001</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>93.3</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>90.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>93.3</v>
+        <v>65</v>
       </c>
       <c r="AS8" t="n">
-        <v>54.8</v>
+        <v>-25</v>
       </c>
       <c r="AT8" t="n">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>-25</v>
+        <v>1.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>72.5</v>
+        <v>1.78</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.6</v>
+        <v>0.33</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.71</v>
+        <v>63</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.33</v>
+        <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="BD8" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>60</v>
+        <v>38.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="BH8" t="n">
         <v>2026</v>
       </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr"/>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
+        </is>
+      </c>
       <c r="BN8" t="inlineStr">
+        <is>
+          <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
         <is>
           <t>Nearly zero-emission living laboratory; no dedicated active cooling.</t>
         </is>
@@ -2597,166 +2572,145 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="J9" t="n">
         <v>62.4723</v>
       </c>
-      <c r="M9" t="n">
+      <c r="K9" t="n">
         <v>6.1799</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
           <t>After 2010</t>
         </is>
+      </c>
+      <c r="R9" t="n">
+        <v>2017</v>
       </c>
       <c r="T9" t="n">
         <v>2017</v>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>2017</v>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>45.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>42.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="AF9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="n">
+      <c r="AU9" t="n">
         <v>0.62</v>
       </c>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="n">
+      <c r="BF9" t="n">
         <v>2024</v>
       </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -2785,166 +2739,145 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="J10" t="n">
         <v>62.47935</v>
       </c>
-      <c r="M10" t="n">
+      <c r="K10" t="n">
         <v>6.17513</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
           <t>After 2010</t>
         </is>
+      </c>
+      <c r="R10" t="n">
+        <v>2015</v>
       </c>
       <c r="T10" t="n">
         <v>2015</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>2015</v>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>42.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>38.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="AF10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
+      <c r="AU10" t="n">
         <v>0.54</v>
       </c>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="n">
+      <c r="BF10" t="n">
         <v>2024</v>
       </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -2973,166 +2906,145 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="J11" t="n">
         <v>62.48371</v>
       </c>
-      <c r="M11" t="n">
+      <c r="K11" t="n">
         <v>6.16263</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
           <t>1960–1990</t>
         </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1984</v>
       </c>
       <c r="T11" t="n">
         <v>1984</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>1984</v>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB11" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>42.3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>28.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="AF11" t="n">
         <v>7.9</v>
       </c>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
+      <c r="AU11" t="n">
         <v>0.38</v>
       </c>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="n">
+      <c r="BF11" t="n">
         <v>2024</v>
       </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3161,166 +3073,145 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="J12" t="n">
         <v>62.48371</v>
       </c>
-      <c r="M12" t="n">
+      <c r="K12" t="n">
         <v>6.14717</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
           <t>After 2010</t>
         </is>
+      </c>
+      <c r="R12" t="n">
+        <v>2012</v>
       </c>
       <c r="T12" t="n">
         <v>2012</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>2012</v>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB12" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>44.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>35.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="AF12" t="n">
         <v>13</v>
       </c>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="n">
+      <c r="AU12" t="n">
         <v>0.62</v>
       </c>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="n">
+      <c r="BF12" t="n">
         <v>2024</v>
       </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3349,166 +3240,145 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="J13" t="n">
         <v>62.47935</v>
       </c>
-      <c r="M13" t="n">
+      <c r="K13" t="n">
         <v>6.13467</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
           <t>1960–1990</t>
         </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1979</v>
       </c>
       <c r="T13" t="n">
         <v>1979</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>1979</v>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>34.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>26.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="AF13" t="n">
         <v>4.1</v>
       </c>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="n">
+      <c r="AU13" t="n">
         <v>0.38</v>
       </c>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="n">
+      <c r="BF13" t="n">
         <v>2024</v>
       </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3537,166 +3407,145 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="J14" t="n">
         <v>62.4723</v>
       </c>
-      <c r="M14" t="n">
+      <c r="K14" t="n">
         <v>6.1299</v>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
           <t>After 2010</t>
         </is>
+      </c>
+      <c r="R14" t="n">
+        <v>2015</v>
       </c>
       <c r="T14" t="n">
         <v>2015</v>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>2015</v>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB14" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>37.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="AF14" t="n">
         <v>7</v>
       </c>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="n">
+      <c r="AU14" t="n">
         <v>0.54</v>
       </c>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="n">
+      <c r="BF14" t="n">
         <v>2024</v>
       </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3725,166 +3574,145 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="J15" t="n">
         <v>62.46525</v>
       </c>
-      <c r="M15" t="n">
+      <c r="K15" t="n">
         <v>6.13467</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
           <t>2000–2010</t>
         </is>
+      </c>
+      <c r="R15" t="n">
+        <v>2002</v>
       </c>
       <c r="T15" t="n">
         <v>2002</v>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>2002</v>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB15" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>38.9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>28.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="AF15" t="n">
         <v>4</v>
       </c>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="n">
+      <c r="AU15" t="n">
         <v>0.38</v>
       </c>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="n">
+      <c r="BF15" t="n">
         <v>2024</v>
       </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3913,166 +3741,145 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="J16" t="n">
         <v>62.46089</v>
       </c>
-      <c r="M16" t="n">
+      <c r="K16" t="n">
         <v>6.14717</v>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
           <t>2000–2010</t>
         </is>
+      </c>
+      <c r="R16" t="n">
+        <v>2006</v>
       </c>
       <c r="T16" t="n">
         <v>2006</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>2006</v>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB16" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>45.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>37.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="AF16" t="n">
         <v>7.9</v>
       </c>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="n">
+      <c r="AU16" t="n">
         <v>0.54</v>
       </c>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="n">
+      <c r="BF16" t="n">
         <v>2024</v>
       </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -4101,166 +3908,145 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="J17" t="n">
         <v>62.46089</v>
       </c>
-      <c r="M17" t="n">
+      <c r="K17" t="n">
         <v>6.16263</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
           <t>2000–2010</t>
         </is>
+      </c>
+      <c r="R17" t="n">
+        <v>2007</v>
       </c>
       <c r="T17" t="n">
         <v>2007</v>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>2007</v>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>38.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>26.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="AF17" t="n">
         <v>6.7</v>
       </c>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="n">
+      <c r="AU17" t="n">
         <v>0.46</v>
       </c>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="n">
+      <c r="BF17" t="n">
         <v>2024</v>
       </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -4289,166 +4075,145 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avendaño et al. (2024)</t>
+          <t>Anonymised</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COLLECTiEF / LifeLine-2050</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anonymised</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Møre og Romsdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ålesund</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Møre og Romsdal</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="J18" t="n">
         <v>62.46525</v>
       </c>
-      <c r="M18" t="n">
+      <c r="K18" t="n">
         <v>6.17513</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Anonymised (spread around city centre)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Anonymised (spread around city centre)</t>
+          <t>Municipal (mixed)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Municipal non-residential (care facility, sport, school or health centre)</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Municipal (mixed)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
           <t>After 2010</t>
         </is>
+      </c>
+      <c r="R18" t="n">
+        <v>2022</v>
       </c>
       <c r="T18" t="n">
         <v>2022</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>2022</v>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Class 6 (20–35%)</t>
+        </is>
+      </c>
       <c r="AB18" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Class 6 (20–35%)</t>
-        </is>
+        <v>44.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>38.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AF18" t="n">
         <v>8.9</v>
       </c>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="n">
+      <c r="AU18" t="n">
         <v>0.54</v>
       </c>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="n">
+      <c r="BF18" t="n">
         <v>2024</v>
       </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>Campodonico Avendano et al. (2024). A novel framework for assessing the smartness and the smart readiness level in highly electrified non-residential buildings: A Norwegian case study. Energy and Buildings 314, 114234</t>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
+          <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -12907,7 +12672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12991,7 +12756,6 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Identity</t>
@@ -13007,11 +12771,6 @@
           <t>Unique building identifier</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13024,7 +12783,6 @@
           <t>Short name</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Identity</t>
@@ -13040,11 +12798,6 @@
           <t>Short label used on charts</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13057,7 +12810,6 @@
           <t>Building</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Identity</t>
@@ -13073,10 +12825,6 @@
           <t>Building name</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13094,7 +12842,6 @@
           <t>Owner / partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Identity</t>
@@ -13110,80 +12857,58 @@
           <t>Owner or project partner</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>source_study</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Source study</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Address</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Study the data comes from</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Street address (or 'Anonymised')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>City</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13193,27 +12918,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Research project</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>City / town</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>municipality</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Municipality</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Location</t>
@@ -13221,32 +12950,31 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Street address (or 'Anonymised')</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Municipality (kommune)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>county</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>County</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Location</t>
@@ -13259,18 +12987,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>City / town</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>County (fylke)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -13279,15 +13004,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>municipality</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Municipality</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Country</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Location</t>
@@ -13300,31 +13024,31 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Municipality (kommune)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Country</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>county</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>County</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Location</t>
@@ -13332,40 +13056,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>County (fylke)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>WGS84 latitude</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Location</t>
@@ -13373,38 +13088,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>WGS84 longitude</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>location_precision</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>°</t>
+          <t>Location precision</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13414,72 +13115,66 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WGS84 latitude</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>How exact the map position is</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>°</t>
+          <t>Building type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WGS84 longitude</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>Building type as reported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>location_precision</t>
+          <t>building_category</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Location precision</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Building category</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -13489,14 +13184,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>How exact the map position is</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+          <t>Harmonised building category</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -13505,15 +13201,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>floor_area_category</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Building type</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Floor area category</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13526,14 +13221,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Building type as reported</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+          <t>Useful floor area class</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -13542,15 +13238,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>building_category</t>
+          <t>floor_area_m2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Building category</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Floor area</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13558,40 +13258,36 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harmonised building category</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Useful floor area (where known)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>floor_area_category</t>
+          <t>construction_period</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Floor area category</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Construction / renovation period</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13604,37 +13300,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Useful floor area class</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Construction or latest renovation period</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>floor_area_m2</t>
+          <t>construction_year</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Floor area</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Construction year</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -13649,35 +13342,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Useful floor area (where known)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Year of construction (where known)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>construction_period</t>
+          <t>latest_renovation_year</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Construction / renovation period</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Latest renovation year</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13685,27 +13374,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Construction or latest renovation period</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>Year of latest major renovation (where known)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -13714,15 +13391,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>construction_year</t>
+          <t>reference_year</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Construction year</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Reference year</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13735,11 +13411,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Year of construction (where known)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+          <t>Construction or latest renovation year; midpoint of period when estimated</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13750,20 +13429,18 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>latest_renovation_year</t>
+          <t>reference_year_estimated</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Latest renovation year</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>Reference year estimated</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13771,36 +13448,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Year of latest major renovation (where known)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>Yes = midpoint of the period</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>reference_year</t>
+          <t>assessed_state</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reference year</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>Assessed state</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13808,44 +13475,31 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Construction or latest renovation year; midpoint of period when estimated</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>State of the building when assessed</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>reference_year_estimated</t>
+          <t>n_sri_domains_assessed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reference year estimated</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>SRI domains assessed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13853,32 +13507,31 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yes = midpoint of the period</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>Number of the 9 SRI technical domains present/assessed</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assessed_state</t>
+          <t>sri_domains_not_assessed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Assessed state</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>SRI domains not assessed</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Building</t>
@@ -13886,34 +13539,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>State of the building when assessed</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>Technical domains absent from the assessment</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>n_sri_domains_assessed</t>
+          <t>epc_label</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRI domains assessed</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>count</t>
+          <t>EPC label</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13923,72 +13566,96 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Number of the 9 SRI technical domains present/assessed</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Energy Performance Certificate label (where known)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sri_domains_not_assessed</t>
+          <t>sri_total_pct</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SRI domains not assessed</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>SRI total score</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>SRI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Technical domains absent from the assessment</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Smart Readiness Indicator total score</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>epc_label</t>
+          <t>sri_class</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPC label</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>SRI class</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>SRI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13998,32 +13665,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Energy Performance Certificate label (where known)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Official 7-class SRI scale (class 1 best)</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sri_total_pct</t>
+          <t>sri_kf1_building_pct</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRI total score</t>
+          <t>SRI KF1 – building (energy performance &amp; operation)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14033,7 +13702,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SRI</t>
+          <t>SRI key functionality</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14043,7 +13712,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smart Readiness Indicator total score</t>
+          <t>Key functionality 1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14075,37 +13744,49 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sri_class</t>
+          <t>sri_kf2_user_pct</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SRI class</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>SRI KF2 – response to user needs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SRI</t>
+          <t>SRI key functionality</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Official 7-class SRI scale (class 1 best)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Key functionality 2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14120,12 +13801,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sri_kf1_building_pct</t>
+          <t>sri_kf3_grid_pct</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SRI KF1 – building (energy performance &amp; operation)</t>
+          <t>SRI KF3 – energy flexibility (grid)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14145,7 +13826,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Key functionality 1</t>
+          <t>Key functionality 3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -14177,12 +13858,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sri_kf2_user_pct</t>
+          <t>sri_impact_energy_efficiency_pct</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SRI KF2 – response to user needs</t>
+          <t>SRI impact – Energy efficiency</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14192,7 +13873,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SRI key functionality</t>
+          <t>SRI impact criteria</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -14202,7 +13883,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Key functionality 2</t>
+          <t>Impact criterion score: Energy efficiency</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -14221,11 +13902,6 @@
         </is>
       </c>
       <c r="J32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -14234,12 +13910,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sri_kf3_grid_pct</t>
+          <t>sri_impact_energy_flexibility_pct</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SRI KF3 – energy flexibility (grid)</t>
+          <t>SRI impact – Energy flexibility and storage</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14249,7 +13925,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SRI key functionality</t>
+          <t>SRI impact criteria</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14259,7 +13935,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Key functionality 3</t>
+          <t>Impact criterion score: Energy flexibility and storage</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14278,11 +13954,6 @@
         </is>
       </c>
       <c r="J33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -14291,12 +13962,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sri_impact_energy_efficiency_pct</t>
+          <t>sri_impact_comfort_pct</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SRI impact – Energy efficiency</t>
+          <t>SRI impact – Comfort</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14316,7 +13987,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Impact criterion score: Energy efficiency</t>
+          <t>Impact criterion score: Comfort</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14339,17 +14010,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sri_impact_energy_flexibility_pct</t>
+          <t>sri_impact_convenience_pct</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SRI impact – Energy flexibility and storage</t>
+          <t>SRI impact – Convenience</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14369,7 +14039,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Impact criterion score: Energy flexibility and storage</t>
+          <t>Impact criterion score: Convenience</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -14392,17 +14062,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sri_impact_comfort_pct</t>
+          <t>sri_impact_health_wellbeing_pct</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRI impact – Comfort</t>
+          <t>SRI impact – Health, well-being and accessibility</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14422,7 +14091,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Impact criterion score: Comfort</t>
+          <t>Impact criterion score: Health, well-being and accessibility</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -14445,17 +14114,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sri_impact_convenience_pct</t>
+          <t>sri_impact_maintenance_pct</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SRI impact – Convenience</t>
+          <t>SRI impact – Maintenance and fault prediction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14475,7 +14143,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Impact criterion score: Convenience</t>
+          <t>Impact criterion score: Maintenance and fault prediction</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -14498,17 +14166,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sri_impact_health_wellbeing_pct</t>
+          <t>sri_impact_information_pct</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRI impact – Health, well-being and accessibility</t>
+          <t>SRI impact – Information to occupants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14528,7 +14195,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Impact criterion score: Health, well-being and accessibility</t>
+          <t>Impact criterion score: Information to occupants</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -14551,17 +14218,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sri_impact_maintenance_pct</t>
+          <t>sri_domain_heating_pct</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SRI impact – Maintenance and fault prediction</t>
+          <t>SRI domain – Heating</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14571,7 +14237,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SRI impact criteria</t>
+          <t>SRI technical domains</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -14581,7 +14247,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Impact criterion score: Maintenance and fault prediction</t>
+          <t>Technical domain score: Heating (can be negative)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -14604,17 +14270,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sri_impact_information_pct</t>
+          <t>sri_domain_dhw_pct</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SRI impact – Information to occupants</t>
+          <t>SRI domain – Domestic hot water</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14624,7 +14289,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SRI impact criteria</t>
+          <t>SRI technical domains</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -14634,7 +14299,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Impact criterion score: Information to occupants</t>
+          <t>Technical domain score: Domestic hot water (can be negative)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -14657,17 +14322,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sri_domain_heating_pct</t>
+          <t>sri_domain_cooling_pct</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SRI domain – Heating</t>
+          <t>SRI domain – Cooling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14687,7 +14351,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Technical domain score: Heating (can be negative)</t>
+          <t>Technical domain score: Cooling (can be negative)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -14710,17 +14374,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sri_domain_dhw_pct</t>
+          <t>sri_domain_ventilation_pct</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SRI domain – Domestic hot water</t>
+          <t>SRI domain – Ventilation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14740,7 +14403,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Technical domain score: Domestic hot water (can be negative)</t>
+          <t>Technical domain score: Ventilation (can be negative)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -14763,17 +14426,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sri_domain_cooling_pct</t>
+          <t>sri_domain_lighting_pct</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SRI domain – Cooling</t>
+          <t>SRI domain – Lighting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14793,7 +14455,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Technical domain score: Cooling (can be negative)</t>
+          <t>Technical domain score: Lighting (can be negative)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -14816,17 +14478,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sri_domain_ventilation_pct</t>
+          <t>sri_domain_envelope_pct</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SRI domain – Ventilation</t>
+          <t>SRI domain – Dynamic building envelope</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14846,7 +14507,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Technical domain score: Ventilation (can be negative)</t>
+          <t>Technical domain score: Dynamic building envelope (can be negative)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -14869,17 +14530,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sri_domain_lighting_pct</t>
+          <t>sri_domain_electricity_pct</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SRI domain – Lighting</t>
+          <t>SRI domain – Electricity</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14899,7 +14559,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Technical domain score: Lighting (can be negative)</t>
+          <t>Technical domain score: Electricity (can be negative)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -14922,17 +14582,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sri_domain_envelope_pct</t>
+          <t>sri_domain_ev_charging_pct</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SRI domain – Dynamic building envelope</t>
+          <t>SRI domain – Electric vehicle charging</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14952,7 +14611,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Technical domain score: Dynamic building envelope (can be negative)</t>
+          <t>Technical domain score: Electric vehicle charging (can be negative)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -14975,17 +14634,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sri_domain_electricity_pct</t>
+          <t>sri_domain_monitoring_control_pct</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SRI domain – Electricity</t>
+          <t>SRI domain – Monitoring and control</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -15005,7 +14663,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Technical domain score: Electricity (can be negative)</t>
+          <t>Technical domain score: Monitoring and control (can be negative)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -15028,27 +14686,26 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sri_domain_ev_charging_pct</t>
+          <t>sbp_level</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SRI domain – Electric vehicle charging</t>
+          <t>SbP level</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>level (−2…4)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SRI technical domains</t>
+          <t>Smart by Powerhouse</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -15058,7 +14715,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Technical domain score: Electric vehicle charging (can be negative)</t>
+          <t>Smart by Powerhouse overall ambition/maturity level</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -15081,27 +14738,31 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sri_domain_monitoring_control_pct</t>
+          <t>sbp_enabling_technology_level</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SRI domain – Monitoring and control</t>
+          <t>SbP level – Enabling technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>level (−2…4)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SRI technical domains</t>
+          <t>Smart by Powerhouse topics</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -15111,7 +14772,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Technical domain score: Monitoring and control (can be negative)</t>
+          <t>SbP topic level: Enabling technology</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -15134,17 +14795,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sbp_level</t>
+          <t>sbp_indoor_environment_level</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SbP level</t>
+          <t>SbP level – Indoor environment and work environment</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15154,7 +14814,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Smart by Powerhouse</t>
+          <t>Smart by Powerhouse topics</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -15164,7 +14824,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smart by Powerhouse overall ambition/maturity level</t>
+          <t>SbP topic level: Indoor environment and work environment</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -15183,11 +14843,6 @@
         </is>
       </c>
       <c r="J50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -15196,12 +14851,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sbp_enabling_technology_level</t>
+          <t>sbp_energy_resources_level</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SbP level – Enabling technology</t>
+          <t>SbP level – Energy and resource utilisation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -15221,7 +14876,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SbP topic level: Enabling technology</t>
+          <t>SbP topic level: Energy and resource utilisation</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -15244,17 +14899,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sbp_indoor_environment_level</t>
+          <t>sbp_safety_reliability_level</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SbP level – Indoor environment and work environment</t>
+          <t>SbP level – Safety and reliability</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15274,7 +14928,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SbP topic level: Indoor environment and work environment</t>
+          <t>SbP topic level: Safety and reliability</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -15297,17 +14951,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sbp_energy_resources_level</t>
+          <t>sbp_adaptability_level</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SbP level – Energy and resource utilisation</t>
+          <t>SbP level – Adaptability</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -15327,7 +14980,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SbP topic level: Energy and resource utilisation</t>
+          <t>SbP topic level: Adaptability</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -15350,22 +15003,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sbp_safety_reliability_level</t>
+          <t>sbp_enabling_technology_pct</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SbP level – Safety and reliability</t>
+          <t>SbP score – Enabling technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>level (−2…4)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -15380,7 +15032,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SbP topic level: Safety and reliability</t>
+          <t>SbP topic percentage of points: Enabling technology</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15403,22 +15055,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sbp_adaptability_level</t>
+          <t>sbp_indoor_environment_pct</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SbP level – Adaptability</t>
+          <t>SbP score – Indoor environment and work environment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>level (−2…4)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -15433,7 +15084,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SbP topic level: Adaptability</t>
+          <t>SbP topic percentage of points: Indoor environment and work environment</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15456,17 +15107,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sbp_enabling_technology_pct</t>
+          <t>sbp_energy_resources_pct</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SbP score – Enabling technology</t>
+          <t>SbP score – Energy and resource utilisation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -15486,7 +15136,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SbP topic percentage of points: Enabling technology</t>
+          <t>SbP topic percentage of points: Energy and resource utilisation</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15509,17 +15159,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sbp_indoor_environment_pct</t>
+          <t>sbp_safety_reliability_pct</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SbP score – Indoor environment and work environment</t>
+          <t>SbP score – Safety and reliability</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15539,7 +15188,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SbP topic percentage of points: Indoor environment and work environment</t>
+          <t>SbP topic percentage of points: Safety and reliability</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15562,17 +15211,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sbp_energy_resources_pct</t>
+          <t>sbp_adaptability_pct</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SbP score – Energy and resource utilisation</t>
+          <t>SbP score – Adaptability</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15592,7 +15240,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SbP topic percentage of points: Energy and resource utilisation</t>
+          <t>SbP topic percentage of points: Adaptability</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -15615,27 +15263,21 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sbp_safety_reliability_pct</t>
+          <t>assessment_year</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SbP score – Safety and reliability</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>%</t>
+          <t>Assessment year</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Smart by Powerhouse topics</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -15645,22 +15287,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SbP topic percentage of points: Safety and reliability</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Year of assessment</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -15668,73 +15295,45 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sbp_adaptability_pct</t>
+          <t>sri_method</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SbP score – Adaptability</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>%</t>
+          <t>SRI method / tool</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Smart by Powerhouse topics</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SbP topic percentage of points: Adaptability</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>SRI calculation method and tool</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>assessment_year</t>
+          <t>sbp_tool</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Assessment year</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>SbP tool</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Metadata</t>
@@ -15742,36 +15341,26 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Year of assessment</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>Smart by Powerhouse tool used</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sri_method</t>
+          <t>detail_available</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRI method / tool</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Detailed results available</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>Metadata</t>
@@ -15779,105 +15368,103 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SRI calculation method and tool</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>Whether domain/impact detail exists</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sbp_tool</t>
+          <t>main_reference</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SbP tool</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Main information reference</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>References</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smart by Powerhouse tool used</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>Main source of the information on this building (short citation)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>detail_available</t>
+          <t>main_reference_url</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Detailed results available</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Main information reference URL</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>References</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Whether domain/impact detail exists</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>Link / DOI of the main reference</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>building_info_reference</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Building information reference</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>References</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -15887,30 +15474,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Source publication</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>Source of the building characteristics (type, size, year, location)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>reference_url</t>
+          <t>building_info_reference_url</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Reference URL</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Building information reference URL</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>References</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -15920,47 +15501,90 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Link / DOI</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>Link / DOI of the building information reference</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>performance_info_reference</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Performance information reference</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Source of the SRI / Smart by Powerhouse results</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>performance_info_reference_url</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Performance information reference URL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Link / DOI of the performance information reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Data notes and caveats</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16015,7 +15639,6 @@
           <t>SINTEF Notes – EDISON D1.1a: SRI and Smart by Powerhouse assessment of pilot buildings (2026)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>EDISON pilots: characteristics (Table 2), totals (Table 3), detailed SRI and SbP results (Appendix A)</t>

--- a/data/smart_buildings_dataset.xlsx
+++ b/data/smart_buildings_dataset.xlsx
@@ -68,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12680,7 +12683,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -12766,9 +12769,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unique building identifier</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unique identifier of the building in this dataset. Prefix EDI- = EDISON pilot buildings; AVE- = buildings from Avendaño et al. (2024). Used to link the 'buildings' and 'sri_detailed' sheets.</t>
         </is>
       </c>
     </row>
@@ -12793,9 +12796,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Short label used on charts</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Short label of the building used on charts, legends and in the table (e.g. the partner name or the anonymised code B01–B10).</t>
         </is>
       </c>
     </row>
@@ -12820,9 +12823,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Building name</t>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Full descriptive name of the building (owner and building / site name, or an anonymised name when the source does not disclose it).</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -12852,9 +12855,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Owner or project partner</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Building owner or project partner that provided the building for the assessment (e.g. DNB, Statsbygg, Ålesund municipality).</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12889,9 +12892,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Street address (or 'Anonymised')</t>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Street address of the building as given in the source or found in the public address register. 'Anonymised' when the source does not disclose the location.</t>
         </is>
       </c>
     </row>
@@ -12916,9 +12919,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>City / town</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>City or town where the building is located.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -12953,9 +12956,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Municipality (kommune)</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Municipality (Norwegian: kommune) where the building is located.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -12985,9 +12988,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>County (fylke)</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>County (Norwegian: fylke) where the building is located, using the county division in force from 2024.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13022,9 +13025,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Country</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Country where the building is located.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -13059,9 +13062,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>WGS84 latitude</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Latitude of the map position, in decimal degrees (WGS84). See 'Location precision' for how exact this position is.</t>
         </is>
       </c>
     </row>
@@ -13091,9 +13094,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>WGS84 longitude</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Longitude of the map position, in decimal degrees (WGS84). See 'Location precision' for how exact this position is.</t>
         </is>
       </c>
     </row>
@@ -13118,9 +13121,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>How exact the map position is</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>How exact the map position is: 'Address' = geocoded street address; 'Approximate' = street, locality or company address that could not be fully verified; 'Anonymised' = the source does not disclose the building, so it is placed near the city centre.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -13150,9 +13153,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Building type as reported</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Type of building as described in the source (e.g. office building, university educational building, logistics distribution centre with cold storage).</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -13182,9 +13185,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Harmonised building category</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Harmonised building category used for filtering and colouring: Office, Education, Logistics, Office / laboratory, Municipal (mixed).</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -13219,9 +13222,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Useful floor area class</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Class of useful floor area as reported in the source (e.g. 1 000 – 10 000 m², &gt; 25 000 m²). Used when the exact floor area is not known.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -13261,9 +13264,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Useful floor area (where known)</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Useful (heated) floor area of the building in square metres, where the exact value is known. Empty when only a floor area class is available.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13298,9 +13301,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Construction or latest renovation period</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Period of construction, or of the latest major renovation if the building has been renovated (e.g. 1960–1990, 2000–2010, after 2010). It reflects the age of the technical building systems.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -13340,9 +13343,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Year of construction (where known)</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Year the building was completed, where known.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -13377,9 +13380,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Year of latest major renovation (where known)</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Year of the latest major renovation or upgrade of the building and its technical systems, where known.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -13409,9 +13412,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Construction or latest renovation year; midpoint of period when estimated</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Year used to plot buildings against time: the latest renovation year if any, otherwise the construction year. When only a period is known, the middle of the period is used (see 'Reference year estimated').</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -13451,9 +13454,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Yes = midpoint of the period</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>'Yes' if the reference year is the midpoint of a construction/renovation period rather than an exact year; 'No' if the exact year is known.</t>
         </is>
       </c>
     </row>
@@ -13478,9 +13481,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>State of the building when assessed</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>State of the building at the time of the assessment: original state as built, current state, or after a renovation (with year).</t>
         </is>
       </c>
     </row>
@@ -13510,9 +13513,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Number of the 9 SRI technical domains present/assessed</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Number of the 9 SRI technical domains (heating, domestic hot water, cooling, ventilation, lighting, dynamic envelope, electricity, EV charging, monitoring and control) that are present in the building and were assessed.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -13542,9 +13545,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Technical domains absent from the assessment</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domains that are not present in the building and were therefore excluded from the assessment (e.g. no active cooling). These domains do not lower the SRI score.</t>
         </is>
       </c>
     </row>
@@ -13569,9 +13572,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Energy Performance Certificate label (where known)</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Energy Performance Certificate label (Norwegian energimerke, A–G) of the building, where known. The EPC rates energy demand and is not directly related to smart readiness.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13611,9 +13614,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Smart Readiness Indicator total score</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Total Smart Readiness Indicator (SRI) score, in % of the maximum achievable for this building. It is the weighted combination of the three key functionalities (building, user, grid) and measures how ready the building's technical systems are to use smart technologies. 100 % = fully smart-ready.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13663,9 +13666,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Official 7-class SRI scale (class 1 best)</t>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>SRI class on the official 7-class scale derived from the total score: class 1 = 90–100 %, class 2 = 80–90 %, class 3 = 65–80 %, class 4 = 50–65 %, class 5 = 35–50 %, class 6 = 20–35 %, class 7 = below 20 %.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -13710,9 +13713,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Key functionality 1</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SRI key functionality 1 – Energy performance and operation of the building, in %. Combines the impact criteria 'Energy efficiency' and 'Maintenance and fault prediction'.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -13767,9 +13770,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Key functionality 2</t>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>SRI key functionality 2 – Response to user needs, in %. Combines the impact criteria 'Comfort', 'Convenience', 'Health, well-being and accessibility' and 'Information to occupants'.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -13824,9 +13827,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Key functionality 3</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SRI key functionality 3 – Energy flexibility, in %: the ability of the building to adapt its energy use to signals from the grid (demand response, load shifting, storage). Equal to the impact criterion 'Energy flexibility and storage'.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13881,9 +13884,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Energy efficiency</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: energy savings enabled by the smart-ready services (e.g. room-by-room temperature control, demand-controlled ventilation, daylight-dependent lighting).</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13933,9 +13936,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Energy flexibility and storage</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: ability to shift or reduce energy demand in response to the grid or prices, and to use on-site storage (thermal or electric).</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13985,9 +13988,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Comfort</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: contribution of the smart-ready services to thermal, visual and acoustic comfort of the occupants.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14037,9 +14040,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Convenience</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: how easy the building is to use and operate – automation, fewer manual interventions, user-friendly control.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -14089,9 +14092,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Health, well-being and accessibility</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: contribution to indoor air quality, health, well-being and accessibility for all occupants (including people with reduced mobility).</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -14141,9 +14144,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Maintenance and fault prediction</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: automated fault detection and diagnosis, monitoring of equipment status and predictive maintenance of the technical systems.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -14193,9 +14196,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Impact criterion score: Information to occupants</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: information given to occupants and facility managers about energy use, indoor conditions and system operation.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -14245,9 +14248,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Technical domain score: Heating (can be negative)</t>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the heating system – emission control (e.g. room/zone control), heat generation (e.g. heat pump control), distribution, storage and response to grid signals. Can be negative when a service level penalises an impact criterion.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -14297,9 +14300,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Technical domain score: Domestic hot water (can be negative)</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the domestic hot water system – control of hot water production and storage, use of renewable sources and response to grid signals. Empty if the domain was not assessed.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -14349,9 +14352,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Technical domain score: Cooling (can be negative)</t>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the cooling system – emission and generation control, interlock with heating, flexibility. Empty if the building has no active cooling.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -14401,9 +14404,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Technical domain score: Ventilation (can be negative)</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the ventilation – demand-controlled air flow, heat recovery control, free cooling and indoor air quality monitoring and feedback.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -14453,9 +14456,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Technical domain score: Lighting (can be negative)</t>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of artificial lighting – occupancy-based control and daylight-dependent dimming.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -14505,9 +14508,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Technical domain score: Dynamic building envelope (can be negative)</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the dynamic building envelope – automated solar shading and window control, and reporting of their status.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -14557,9 +14560,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Technical domain score: Electricity (can be negative)</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the electricity system – on-site generation (e.g. PV), electricity storage, optimisation of self-consumption, and reporting.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -14609,9 +14612,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Technical domain score: Electric vehicle charging (can be negative)</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of electric vehicle charging – charging capacity, smart / grid-balancing charging and connectivity. Often negative: uncontrolled charging adds peak load and is penalised in the energy flexibility criterion.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -14661,9 +14664,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Technical domain score: Monitoring and control (can be negative)</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of monitoring and control – central building automation, run-time management, fault detection, occupancy detection, reporting and integration with the smart grid.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -14713,9 +14716,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse overall ambition/maturity level</t>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Overall Smart by Powerhouse (SbP) ambition / maturity level of the building, on the SINTEF tool scale from −2 to 4: −2 No technological equipment, −1 Pre-automated, 0 Automated (today's standard), 1 Smart ready, 2 Smart standard, 3 Smart predictive, 4 Smart cognitive. Decimal values lie between levels.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -14770,9 +14773,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>SbP topic level: Enabling technology</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Enabling technology': digital infrastructure such as building automation, sensors, open data standards and interfaces (APIs), BIM / digital twin, connectivity and indoor positioning.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14822,9 +14825,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>SbP topic level: Indoor environment and work environment</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Indoor climate and working environment': thermal comfort, air quality, lighting, acoustics and ergonomics, and how the building adapts them to the users.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14874,9 +14877,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>SbP topic level: Energy and resource utilisation</t>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Energy and resource utilisation': energy efficiency, energy flexibility and interaction with the grid, and efficient use of resources (e.g. waste management).</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -14926,9 +14929,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>SbP topic level: Safety and reliability</t>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Safety, security and reliability': physical safety and security (access, fire, flooding and other hazards), cyber security, data privacy and reliable operation.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -14978,9 +14981,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>SbP topic level: Adaptability</t>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Adaptability': ability of the building, its spaces and its systems to adapt to new uses, users and technologies, and efficient use of floor space.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -15030,9 +15033,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>SbP topic percentage of points: Enabling technology</t>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Enabling technology', in %. The topic level is derived from this percentage.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15082,9 +15085,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>SbP topic percentage of points: Indoor environment and work environment</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Indoor climate and working environment', in %. The topic level is derived from this percentage.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15134,9 +15137,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>SbP topic percentage of points: Energy and resource utilisation</t>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Energy and resource utilisation', in %. The topic level is derived from this percentage.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15186,9 +15189,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>SbP topic percentage of points: Safety and reliability</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Safety, security and reliability', in %. The topic level is derived from this percentage.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15238,9 +15241,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>SbP topic percentage of points: Adaptability</t>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Adaptability', in %. The topic level is derived from this percentage.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -15285,9 +15288,9 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Year of assessment</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Year in which the SRI and Smart by Powerhouse assessments of the building were carried out.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -15317,9 +15320,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>SRI calculation method and tool</t>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>SRI calculation method and tool used (e.g. official EC calculation sheet v4.5, U-CERT online tool, or Norway-specific weighting factors). Scores obtained with different methods are not strictly comparable.</t>
         </is>
       </c>
     </row>
@@ -15344,9 +15347,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse tool used</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Tool and scale used for the Smart by Powerhouse assessment (SINTEF spreadsheet tool with the −2 to 4 scale, or a modified version).</t>
         </is>
       </c>
     </row>
@@ -15371,9 +15374,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Whether domain/impact detail exists</t>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>'Yes' if detailed results (SRI impact criteria, technical domains, domain × impact matrix and SbP topics) are available for the building; 'No' if only total scores and key functionalities are published.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -15403,9 +15406,9 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Main source of the information on this building (short citation)</t>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Main source of the information on this building (short citation). The full reference is listed on the About page.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -15445,9 +15448,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Link / DOI of the main reference</t>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Web link or DOI of the main information reference, where available.</t>
         </is>
       </c>
     </row>
@@ -15472,9 +15475,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Source of the building characteristics (type, size, year, location)</t>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Source of the building characteristics: type, size, construction/renovation year and location.</t>
         </is>
       </c>
     </row>
@@ -15499,9 +15502,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Link / DOI of the building information reference</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Web link or DOI of the building information reference, where available.</t>
         </is>
       </c>
     </row>
@@ -15526,9 +15529,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Source of the SRI / Smart by Powerhouse results</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Source of the performance results: SRI scores and Smart by Powerhouse levels.</t>
         </is>
       </c>
     </row>
@@ -15553,9 +15556,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Link / DOI of the performance information reference</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Web link or DOI of the performance information reference, where available.</t>
         </is>
       </c>
     </row>
@@ -15580,9 +15583,9 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Data notes and caveats</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Data notes and caveats for this building (inconsistencies in the source, approximations, comparability issues).</t>
         </is>
       </c>
     </row>

--- a/data/smart_buildings_dataset.xlsx
+++ b/data/smart_buildings_dataset.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,14 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +29,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,10 +57,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -70,7 +77,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -78,7 +85,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -464,14 +471,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sheet 'data_dictionary' drives the web app: label, unit, group and flags (Y) for map_size, map_color, xy, filter, hover.</t>
+          <t>Sheet 'data_dictionary' drives the web app: label, unit, group, dtype (numeric / categorical / text) and description of every column. All parameters appear in the app dropdowns according to their dtype; 'hover' = Y shows the parameter in every map/plot hover pop-up.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>To add a parameter: add a column in 'buildings' AND a row in 'data_dictionary'. It then appears in the app dropdowns automatically.</t>
+          <t>To add a parameter: add a column in 'buildings' AND a row in 'data_dictionary' (with its dtype). It then appears in the app dropdowns automatically; it is listed as '(no data yet)' until a building has a value.</t>
         </is>
       </c>
     </row>
@@ -514,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:CP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -525,12 +532,12 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="10"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="15"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
@@ -542,52 +549,75 @@
     <col width="24" customWidth="1" min="23" max="23"/>
     <col width="26" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
-    <col width="18" customWidth="1" min="30" max="30"/>
-    <col width="34" customWidth="1" min="31" max="31"/>
-    <col width="35" customWidth="1" min="32" max="32"/>
-    <col width="24" customWidth="1" min="33" max="33"/>
-    <col width="28" customWidth="1" min="34" max="34"/>
-    <col width="33" customWidth="1" min="35" max="35"/>
-    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="30"/>
+    <col width="25" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="21" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="37"/>
     <col width="28" customWidth="1" min="37" max="37"/>
-    <col width="24" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="24" customWidth="1" min="40" max="40"/>
-    <col width="28" customWidth="1" min="41" max="41"/>
-    <col width="25" customWidth="1" min="42" max="42"/>
-    <col width="25" customWidth="1" min="43" max="43"/>
-    <col width="28" customWidth="1" min="44" max="44"/>
-    <col width="28" customWidth="1" min="45" max="45"/>
-    <col width="35" customWidth="1" min="46" max="46"/>
-    <col width="11" customWidth="1" min="47" max="47"/>
-    <col width="31" customWidth="1" min="48" max="48"/>
-    <col width="30" customWidth="1" min="49" max="49"/>
-    <col width="28" customWidth="1" min="50" max="50"/>
-    <col width="30" customWidth="1" min="51" max="51"/>
-    <col width="24" customWidth="1" min="52" max="52"/>
-    <col width="29" customWidth="1" min="53" max="53"/>
-    <col width="28" customWidth="1" min="54" max="54"/>
-    <col width="26" customWidth="1" min="55" max="55"/>
-    <col width="28" customWidth="1" min="56" max="56"/>
-    <col width="22" customWidth="1" min="57" max="57"/>
-    <col width="17" customWidth="1" min="58" max="58"/>
-    <col width="60" customWidth="1" min="59" max="59"/>
-    <col width="46" customWidth="1" min="60" max="60"/>
-    <col width="18" customWidth="1" min="61" max="61"/>
-    <col width="60" customWidth="1" min="62" max="62"/>
-    <col width="47" customWidth="1" min="63" max="63"/>
-    <col width="60" customWidth="1" min="64" max="64"/>
-    <col width="47" customWidth="1" min="65" max="65"/>
-    <col width="60" customWidth="1" min="66" max="66"/>
-    <col width="60" customWidth="1" min="67" max="67"/>
-    <col width="60" customWidth="1" min="68" max="68"/>
-    <col width="30" customWidth="1" min="69" max="69"/>
-    <col width="45" customWidth="1" min="70" max="70"/>
-    <col width="30" customWidth="1" min="71" max="71"/>
+    <col width="31" customWidth="1" min="38" max="38"/>
+    <col width="31" customWidth="1" min="39" max="39"/>
+    <col width="32" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
+    <col width="22" customWidth="1" min="42" max="43"/>
+    <col width="32" customWidth="1" min="43" max="43"/>
+    <col width="27" customWidth="1" min="44" max="45"/>
+    <col width="29" customWidth="1" min="45" max="45"/>
+    <col width="38" customWidth="1" min="46" max="46"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
+    <col width="19" customWidth="1" min="48" max="48"/>
+    <col width="19" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="50" max="50"/>
+    <col width="27" customWidth="1" min="51" max="51"/>
+    <col width="15" customWidth="1" min="52" max="52"/>
+    <col width="18" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="56" max="56"/>
+    <col width="34" customWidth="1" min="57" max="57"/>
+    <col width="35" customWidth="1" min="58" max="58"/>
+    <col width="24" customWidth="1" min="59" max="59"/>
+    <col width="28" customWidth="1" min="60" max="60"/>
+    <col width="33" customWidth="1" min="61" max="61"/>
+    <col width="28" customWidth="1" min="62" max="62"/>
+    <col width="28" customWidth="1" min="63" max="63"/>
+    <col width="24" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="65" max="65"/>
+    <col width="24" customWidth="1" min="66" max="68"/>
+    <col width="28" customWidth="1" min="67" max="67"/>
+    <col width="25" customWidth="1" min="68" max="68"/>
+    <col width="25" customWidth="1" min="69" max="69"/>
+    <col width="28" customWidth="1" min="70" max="70"/>
+    <col width="28" customWidth="1" min="71" max="71"/>
+    <col width="35" customWidth="1" min="72" max="72"/>
+    <col width="11" customWidth="1" min="73" max="73"/>
+    <col width="31" customWidth="1" min="74" max="74"/>
+    <col width="30" customWidth="1" min="75" max="75"/>
+    <col width="28" customWidth="1" min="76" max="76"/>
+    <col width="30" customWidth="1" min="77" max="77"/>
+    <col width="24" customWidth="1" min="78" max="78"/>
+    <col width="29" customWidth="1" min="79" max="79"/>
+    <col width="28" customWidth="1" min="80" max="80"/>
+    <col width="26" customWidth="1" min="81" max="81"/>
+    <col width="28" customWidth="1" min="82" max="82"/>
+    <col width="22" customWidth="1" min="83" max="83"/>
+    <col width="27" customWidth="1" min="84" max="84"/>
+    <col width="60" customWidth="1" min="85" max="85"/>
+    <col width="46" customWidth="1" min="86" max="86"/>
+    <col width="18" customWidth="1" min="87" max="87"/>
+    <col width="60" customWidth="1" min="88" max="88"/>
+    <col width="47" customWidth="1" min="89" max="89"/>
+    <col width="60" customWidth="1" min="90" max="90"/>
+    <col width="60" customWidth="1" min="91" max="91"/>
+    <col width="60" customWidth="1" min="92" max="92"/>
+    <col width="47" customWidth="1" min="93" max="93"/>
+    <col width="60" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -718,215 +748,345 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>performance_reference_year</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>primary_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>final_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>electricity_use_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>heating_demand_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>cooling_demand_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dhw_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lighting_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>hvac_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>peak_heating_load_w_m2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>peak_cooling_load_w_m2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>peak_electricity_load_w_m2</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>peak_final_energy_demand_w_m2</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>renewable_generation_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>renewable_self_consumption_pct</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>grid_import_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>grid_export_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>operational_carbon_kgco2e_m2yr</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>embodied_carbon_kgco2e_m2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>whole_life_carbon_kgco2e_m2</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>whole_life_carbon_study_period_years</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>carbon_intensity_energy_kgco2e_kwh</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>water_use_m3_m2yr</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>u_value_avg_w_m2k</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cost_eur_m2yr</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>occupant_satisfaction_pct</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>sri_total_pct</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sri_class</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sri_kf1_building_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sri_kf2_user_pct</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sri_kf3_grid_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_energy_efficiency_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_energy_flexibility_pct</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_comfort_pct</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_convenience_pct</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_health_wellbeing_pct</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_maintenance_pct</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>sri_impact_information_pct</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_heating_pct</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_dhw_pct</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_cooling_pct</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_ventilation_pct</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_lighting_pct</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_envelope_pct</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_electricity_pct</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_ev_charging_pct</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>sri_domain_monitoring_control_pct</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>sbp_level</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>sbp_enabling_technology_level</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>sbp_indoor_environment_level</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>sbp_energy_resources_level</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>sbp_safety_reliability_level</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>sbp_adaptability_level</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>sbp_enabling_technology_pct</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>sbp_indoor_environment_pct</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>sbp_energy_resources_pct</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>sbp_safety_reliability_pct</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>sbp_adaptability_pct</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>assessment_year</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>smartness_assessment_year</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>sri_method</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>sbp_tool</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>detail_available</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>main_reference</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>main_reference_url</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>building_info_reference</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>building_info_reference_url</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>performance_info_reference</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>performance_info_reference_url</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1030,135 +1190,135 @@
           <t>Domestic hot water</t>
         </is>
       </c>
-      <c r="Z2" t="n">
+      <c r="AZ2" t="n">
         <v>62.6</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Class 4 (50–65%)</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="BB2" t="n">
         <v>62.4</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="BC2" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="BD2" t="n">
         <v>49.5</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="BE2" t="n">
         <v>65.5</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="BF2" t="n">
         <v>49.5</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="BG2" t="n">
         <v>83.2</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="BH2" t="n">
         <v>72.8</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="BI2" t="n">
         <v>86.2</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="BJ2" t="n">
         <v>59.4</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="BK2" t="n">
         <v>61.5</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="BL2" t="n">
         <v>55.2</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="BN2" t="n">
         <v>81.3</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="BO2" t="n">
         <v>70.2</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="BP2" t="n">
         <v>93.3</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BQ2" t="n">
         <v>54</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BR2" t="n">
         <v>55.6</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BS2" t="n">
         <v>-25</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BT2" t="n">
         <v>73</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BU2" t="n">
         <v>0.97</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BV2" t="n">
         <v>1</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BW2" t="n">
         <v>1</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BX2" t="n">
         <v>0.4</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BY2" t="n">
         <v>1.57</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BZ2" t="n">
         <v>0.33</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="CA2" t="n">
         <v>50</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="CB2" t="n">
         <v>50</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="CC2" t="n">
         <v>40</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="CD2" t="n">
         <v>59.5</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="CE2" t="n">
         <v>38.9</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="CF2" t="n">
         <v>2026</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>Report Table 2 states 'After 2010 (C)' while Table 3 and Figure 9 use 2000–2010; 2000–2010 kept. Exact street number to verify.</t>
         </is>
@@ -1257,138 +1417,138 @@
       <c r="W3" t="n">
         <v>9</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AZ3" t="n">
         <v>33.6</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="BB3" t="n">
         <v>42.7</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="BC3" t="n">
         <v>42</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="BD3" t="n">
         <v>16.2</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="BE3" t="n">
         <v>48.5</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="BF3" t="n">
         <v>16.2</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="BG3" t="n">
         <v>47</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="BH3" t="n">
         <v>36.1</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="BI3" t="n">
         <v>41.2</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="BJ3" t="n">
         <v>36.8</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="BK3" t="n">
         <v>43.5</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="BL3" t="n">
         <v>39.8</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="BM3" t="n">
         <v>36.7</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="BN3" t="n">
         <v>23.9</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="BO3" t="n">
         <v>50.9</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="BP3" t="n">
         <v>22</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="BQ3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BR3" t="n">
         <v>5.6</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BS3" t="n">
         <v>-13.9</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BT3" t="n">
         <v>37.6</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BU3" t="n">
         <v>0.48</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BV3" t="n">
         <v>0.67</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BW3" t="n">
         <v>0.2</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BX3" t="n">
         <v>0.2</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BY3" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BZ3" t="n">
         <v>0</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="CA3" t="n">
         <v>44.4</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="CB3" t="n">
         <v>36.7</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="CC3" t="n">
         <v>36.7</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="CD3" t="n">
         <v>47.6</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="CE3" t="n">
         <v>33.3</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="CF3" t="n">
         <v>2026</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>Campus address used; assessed building within campus not specified.</t>
         </is>
@@ -1492,135 +1652,135 @@
           <t>Domestic hot water</t>
         </is>
       </c>
-      <c r="Z4" t="n">
+      <c r="AZ4" t="n">
         <v>14.8</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Class 7 (&lt;20%)</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="BB4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="BC4" t="n">
         <v>20.7</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="BD4" t="n">
         <v>1.1</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="BE4" t="n">
         <v>30.9</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="BF4" t="n">
         <v>1.1</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="BG4" t="n">
         <v>37.4</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="BH4" t="n">
         <v>19.7</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="BI4" t="n">
         <v>19.2</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="BJ4" t="n">
         <v>14.6</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="BK4" t="n">
         <v>6.5</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="BL4" t="n">
         <v>22.2</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="BN4" t="n">
         <v>23.4</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="BO4" t="n">
         <v>27.9</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="BP4" t="n">
         <v>29.3</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="BQ4" t="n">
         <v>16</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BR4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BS4" t="n">
         <v>-27.8</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BT4" t="n">
         <v>6.9</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BU4" t="n">
         <v>-1.28</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BV4" t="n">
         <v>-2</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BW4" t="n">
         <v>-1.8</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BX4" t="n">
         <v>-2</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BY4" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BZ4" t="n">
         <v>-2</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="CA4" t="n">
         <v>0</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="CB4" t="n">
         <v>3.3</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="CC4" t="n">
         <v>0</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="CD4" t="n">
         <v>47.6</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="CE4" t="n">
         <v>0</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="CF4" t="n">
         <v>2026</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>Address from public company directories, not from the report.</t>
         </is>
@@ -1719,133 +1879,133 @@
       <c r="W5" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AZ5" t="n">
         <v>32.6</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="BB5" t="n">
         <v>42.3</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="BC5" t="n">
         <v>48.3</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="BD5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="BE5" t="n">
         <v>50.4</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="BF5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="BG5" t="n">
         <v>53.7</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="BH5" t="n">
         <v>42.9</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="BI5" t="n">
         <v>53.1</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="BJ5" t="n">
         <v>34.1</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="BK5" t="n">
         <v>43.4</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="BL5" t="n">
         <v>26.4</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BM5" t="n">
         <v>61.1</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BN5" t="n">
         <v>43.3</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="BO5" t="n">
         <v>57.6</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="BP5" t="n">
         <v>29.3</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="BQ5" t="n">
         <v>36.5</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BR5" t="n">
         <v>25</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BS5" t="n">
         <v>27.8</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BT5" t="n">
         <v>38.4</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BU5" t="n">
         <v>0.59</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BV5" t="n">
         <v>0.89</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BW5" t="n">
         <v>0.2</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BX5" t="n">
         <v>0.6</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BY5" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BZ5" t="n">
         <v>-0.33</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="CA5" t="n">
         <v>48.1</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="CB5" t="n">
         <v>36.7</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="CC5" t="n">
         <v>43.3</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="CD5" t="n">
         <v>47.6</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="CE5" t="n">
         <v>27.8</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="CF5" t="n">
         <v>2026</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
@@ -1947,138 +2107,138 @@
       <c r="W6" t="n">
         <v>9</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AZ6" t="n">
         <v>34.2</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="BB6" t="n">
         <v>53.3</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="BC6" t="n">
         <v>45.4</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="BD6" t="n">
         <v>4</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="BE6" t="n">
         <v>67.3</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="BF6" t="n">
         <v>4</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="BG6" t="n">
         <v>54.3</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="BH6" t="n">
         <v>41</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="BI6" t="n">
         <v>49.1</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="BJ6" t="n">
         <v>39.3</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="BK6" t="n">
         <v>37.1</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="BL6" t="n">
         <v>43.5</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BM6" t="n">
         <v>68.3</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="BN6" t="n">
         <v>32.4</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="BO6" t="n">
         <v>76</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="BP6" t="n">
         <v>29.3</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="BQ6" t="n">
         <v>0</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BR6" t="n">
         <v>25</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BS6" t="n">
         <v>-13.9</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BT6" t="n">
         <v>25.5</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BU6" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BV6" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BW6" t="n">
         <v>0</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BX6" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BY6" t="n">
         <v>0</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BZ6" t="n">
         <v>-0.33</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="CA6" t="n">
         <v>24.1</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="CB6" t="n">
         <v>33.3</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="CC6" t="n">
         <v>33.3</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="CD6" t="n">
         <v>33.3</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="CE6" t="n">
         <v>27.8</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="CF6" t="n">
         <v>2026</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>Constructed 2000–2010, latest renovation 2020 (report Table 2).</t>
         </is>
@@ -2177,138 +2337,138 @@
       <c r="W7" t="n">
         <v>9</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AZ7" t="n">
         <v>73.7</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>Class 3 (65–80%)</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="BB7" t="n">
         <v>64.8</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="BC7" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="BD7" t="n">
         <v>86.5</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="BE7" t="n">
         <v>79.5</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="BF7" t="n">
         <v>86.5</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="BG7" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="BH7" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="BI7" t="n">
         <v>68.5</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="BJ7" t="n">
         <v>50</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="BK7" t="n">
         <v>70.5</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="BL7" t="n">
         <v>77.5</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BM7" t="n">
         <v>57.4</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="BN7" t="n">
         <v>89</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="BO7" t="n">
         <v>70</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="BP7" t="n">
         <v>82</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="BQ7" t="n">
         <v>19.8</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BR7" t="n">
         <v>74.3</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BS7" t="n">
         <v>-25</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BT7" t="n">
         <v>63</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BU7" t="n">
         <v>1.24</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BV7" t="n">
         <v>1.67</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BW7" t="n">
         <v>0.4</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BX7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BY7" t="n">
         <v>0.86</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BZ7" t="n">
         <v>1.33</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="CA7" t="n">
         <v>61.1</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="CB7" t="n">
         <v>40</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="CC7" t="n">
         <v>63.3</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="CD7" t="n">
         <v>47.6</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="CE7" t="n">
         <v>55.6</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="CF7" t="n">
         <v>2026</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>Address not found in the Kartverket register; positioned at Vagle locality.</t>
         </is>
@@ -2418,135 +2578,135 @@
           <t>Cooling</t>
         </is>
       </c>
-      <c r="Z8" t="n">
+      <c r="AZ8" t="n">
         <v>62.9</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>Class 4 (50–65%)</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="BB8" t="n">
         <v>68</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="BC8" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="BD8" t="n">
         <v>44.4</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="BE8" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="BF8" t="n">
         <v>44.4</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="BG8" t="n">
         <v>85.2</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="BH8" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="BI8" t="n">
         <v>80.8</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="BJ8" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="BK8" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="BL8" t="n">
         <v>51.9</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="BM8" t="n">
         <v>48.5</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="BO8" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="BP8" t="n">
         <v>93.3</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="BQ8" t="n">
         <v>54.8</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BR8" t="n">
         <v>65</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BS8" t="n">
         <v>-25</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BT8" t="n">
         <v>72.5</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BU8" t="n">
         <v>1.45</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BV8" t="n">
         <v>1.78</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BW8" t="n">
         <v>1</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BX8" t="n">
         <v>1.6</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BY8" t="n">
         <v>1.71</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BZ8" t="n">
         <v>0.33</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="CA8" t="n">
         <v>63</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="CB8" t="n">
         <v>50</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="CC8" t="n">
         <v>60</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="CD8" t="n">
         <v>61.9</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="CE8" t="n">
         <v>38.9</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="CF8" t="n">
         <v>2026</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>SRI method A/B, EC calculation sheet v4.5 (cross-checked with U-CERT)</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>SINTEF SbP spreadsheet tool (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a, SRI and Smart by Powerhouse assessment (2026)</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 2 and section 'Presentation of the pilot building cases'</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>SINTEF Notes – EDISON D1.1a (2026): Table 3 and Appendix A (detailed SRI and SbP results)</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>Nearly zero-emission living laboratory; no dedicated active cooling.</t>
         </is>
@@ -2645,75 +2805,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z9" t="n">
+      <c r="AZ9" t="n">
         <v>30.6</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB9" t="n">
+      <c r="BB9" t="n">
         <v>45.6</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="BC9" t="n">
         <v>42.1</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="BD9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BU9" t="n">
         <v>0.62</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="CF9" t="n">
         <v>2024</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -2812,75 +2972,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z10" t="n">
+      <c r="AZ10" t="n">
         <v>31.7</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB10" t="n">
+      <c r="BB10" t="n">
         <v>42.3</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="BC10" t="n">
         <v>38.3</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="BD10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BU10" t="n">
         <v>0.54</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="CF10" t="n">
         <v>2024</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -2979,75 +3139,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z11" t="n">
+      <c r="AZ11" t="n">
         <v>26.3</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB11" t="n">
+      <c r="BB11" t="n">
         <v>42.3</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="BC11" t="n">
         <v>28.6</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="BD11" t="n">
         <v>7.9</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BU11" t="n">
         <v>0.38</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="CF11" t="n">
         <v>2024</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3146,75 +3306,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z12" t="n">
+      <c r="AZ12" t="n">
         <v>31</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB12" t="n">
+      <c r="BB12" t="n">
         <v>44.3</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="BC12" t="n">
         <v>35.7</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="BD12" t="n">
         <v>13</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BU12" t="n">
         <v>0.62</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="CF12" t="n">
         <v>2024</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3313,75 +3473,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z13" t="n">
+      <c r="AZ13" t="n">
         <v>21.6</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB13" t="n">
+      <c r="BB13" t="n">
         <v>34.6</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="BC13" t="n">
         <v>26.1</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="BD13" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BU13" t="n">
         <v>0.38</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="CF13" t="n">
         <v>2024</v>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="CG13" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="CH13" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="CK13" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="CL13" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="CM13" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="CN13" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="CO13" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="CP13" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3480,75 +3640,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z14" t="n">
+      <c r="AZ14" t="n">
         <v>28.9</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB14" t="n">
+      <c r="BB14" t="n">
         <v>42</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="BC14" t="n">
         <v>37.7</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="BD14" t="n">
         <v>7</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BU14" t="n">
         <v>0.54</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="CF14" t="n">
         <v>2024</v>
       </c>
-      <c r="BG14" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH14" t="inlineStr">
+      <c r="CH14" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
+      <c r="CK14" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL14" t="inlineStr">
+      <c r="CL14" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM14" t="inlineStr">
+      <c r="CM14" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="CN14" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="CO14" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
+      <c r="CP14" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3647,75 +3807,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z15" t="n">
+      <c r="AZ15" t="n">
         <v>23.9</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB15" t="n">
+      <c r="BB15" t="n">
         <v>38.9</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="BC15" t="n">
         <v>28.9</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="BD15" t="n">
         <v>4</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BU15" t="n">
         <v>0.38</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="CF15" t="n">
         <v>2024</v>
       </c>
-      <c r="BG15" t="inlineStr">
+      <c r="CG15" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH15" t="inlineStr">
+      <c r="CH15" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="CK15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
+      <c r="CL15" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM15" t="inlineStr">
+      <c r="CM15" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="CN15" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="CO15" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
+      <c r="CP15" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3814,75 +3974,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z16" t="n">
+      <c r="AZ16" t="n">
         <v>30.2</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB16" t="n">
+      <c r="BB16" t="n">
         <v>45.4</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="BC16" t="n">
         <v>37.4</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="BD16" t="n">
         <v>7.9</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BU16" t="n">
         <v>0.54</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="CF16" t="n">
         <v>2024</v>
       </c>
-      <c r="BG16" t="inlineStr">
+      <c r="CG16" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
+      <c r="CH16" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="CK16" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
+      <c r="CL16" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM16" t="inlineStr">
+      <c r="CM16" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="CN16" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="CO16" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
+      <c r="CP16" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -3981,75 +4141,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z17" t="n">
+      <c r="AZ17" t="n">
         <v>24</v>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="BA17" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB17" t="n">
+      <c r="BB17" t="n">
         <v>38.9</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="BC17" t="n">
         <v>26.6</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="BD17" t="n">
         <v>6.7</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BU17" t="n">
         <v>0.46</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="CF17" t="n">
         <v>2024</v>
       </c>
-      <c r="BG17" t="inlineStr">
+      <c r="CG17" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH17" t="inlineStr">
+      <c r="CH17" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="CK17" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr">
+      <c r="CL17" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM17" t="inlineStr">
+      <c r="CM17" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="CN17" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="CO17" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
+      <c r="CP17" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -4148,75 +4308,75 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="Z18" t="n">
+      <c r="AZ18" t="n">
         <v>30.5</v>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>Class 6 (20–35%)</t>
         </is>
       </c>
-      <c r="AB18" t="n">
+      <c r="BB18" t="n">
         <v>44.5</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="BC18" t="n">
         <v>38.1</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="BD18" t="n">
         <v>8.9</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BU18" t="n">
         <v>0.54</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="CF18" t="n">
         <v>2024</v>
       </c>
-      <c r="BG18" t="inlineStr">
+      <c r="CG18" t="inlineStr">
         <is>
           <t>SRI with Norway-specific weighting factors (Avendaño et al. 2024)</t>
         </is>
       </c>
-      <c r="BH18" t="inlineStr">
+      <c r="CH18" t="inlineStr">
         <is>
           <t>Modified Smart by Powerhouse (scale −2 to 4)</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="CK18" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
+      <c r="CL18" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (construction years); REHVA Journal 05/2024, pp. 23–26 (location and building categories)</t>
         </is>
       </c>
-      <c r="BM18" t="inlineStr">
+      <c r="CM18" t="inlineStr">
         <is>
           <t>https://www.rehva.eu/rehva-journal/chapter/the-smart-by-powerhouse-sri-framework-towards-a-smarter-norwegian-building-stock</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="CN18" t="inlineStr">
         <is>
           <t>Campodonico Avendaño et al. (2024), Energy and Buildings 314, 114234 (SRI and SbP scores); REHVA Journal 05/2024, Table 1 (SRI key functionalities)</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="CO18" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.enbuild.2024.114234</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
+      <c r="CP18" t="inlineStr">
         <is>
           <t>Only totals and key functionalities published per building. SRI uses customised weights: compare with care.</t>
         </is>
@@ -12675,7 +12835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12686,9 +12846,7 @@
     <col width="90" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="9" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12724,31 +12882,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>map_size</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>map_color</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>xy</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>hover</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>building_id</t>
@@ -12775,7 +12913,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>short_name</t>
@@ -12802,7 +12940,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>building_name</t>
@@ -12828,13 +12966,13 @@
           <t>Full descriptive name of the building (owner and building / site name, or an anonymised name when the source does not disclose it).</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>owner_partner</t>
@@ -12860,18 +12998,8 @@
           <t>Building owner or project partner that provided the building for the assessment (e.g. DNB, Statsbygg, Ålesund municipality).</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>address</t>
@@ -12924,12 +13052,7 @@
           <t>City or town where the building is located.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -12961,13 +13084,8 @@
           <t>Municipality (Norwegian: kommune) where the building is located.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>county</t>
@@ -12991,16 +13109,6 @@
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>County (Norwegian: fylke) where the building is located, using the county division in force from 2024.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
     </row>
@@ -13030,293 +13138,248 @@
           <t>Country where the building is located.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Latitude of the map position, in decimal degrees (WGS84). See 'Location precision' for how exact this position is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Longitude of the map position, in decimal degrees (WGS84). See 'Location precision' for how exact this position is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>location_precision</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Location precision</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>How exact the map position is: 'Address' = geocoded street address; 'Approximate' = street, locality or company address that could not be fully verified; 'Anonymised' = the source does not disclose the building, so it is placed near the city centre.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Building type</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Type of building as described in the source (e.g. office building, university educational building, logistics distribution centre with cold storage).</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>building_category</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Building category</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Harmonised building category used for filtering and colouring: Office, Education, Logistics, Office / laboratory, Municipal (mixed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>floor_area_category</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Floor area category</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Class of useful floor area as reported in the source (e.g. 1 000 – 10 000 m², &gt; 25 000 m²). Used when the exact floor area is not known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>floor_area_m2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Floor area</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Latitude of the map position, in decimal degrees (WGS84). See 'Location precision' for how exact this position is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Longitude of the map position, in decimal degrees (WGS84). See 'Location precision' for how exact this position is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>location_precision</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Location precision</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Useful (conditioned) floor area of the building in square metres, where the exact value is known. Empty when only a floor area class is available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>construction_period</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Construction / renovation period</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>How exact the map position is: 'Address' = geocoded street address; 'Approximate' = street, locality or company address that could not be fully verified; 'Anonymised' = the source does not disclose the building, so it is placed near the city centre.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>building_type</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Building type</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Type of building as described in the source (e.g. office building, university educational building, logistics distribution centre with cold storage).</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>building_category</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Building category</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Harmonised building category used for filtering and colouring: Office, Education, Logistics, Office / laboratory, Municipal (mixed).</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>floor_area_category</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Floor area category</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Class of useful floor area as reported in the source (e.g. 1 000 – 10 000 m², &gt; 25 000 m²). Used when the exact floor area is not known.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>floor_area_m2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Floor area</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Useful (heated) floor area of the building in square metres, where the exact value is known. Empty when only a floor area class is available.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>construction_period</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Construction / renovation period</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Period of construction, or of the latest major renovation if the building has been renovated (e.g. 1960–1990, 2000–2010, after 2010). It reflects the age of the technical building systems.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -13348,2242 +13411,2374 @@
           <t>Year the building was completed, where known.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>latest_renovation_year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Latest renovation year</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Year of the latest major renovation or upgrade of the building and its technical systems, where known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>reference_year</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Reference year</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Year used to plot buildings against time: the latest renovation year if any, otherwise the construction year. When only a period is known, the middle of the period is used (see 'Reference year estimated').</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>reference_year_estimated</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Reference year estimated</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>'Yes' if the reference year is the midpoint of a construction/renovation period rather than an exact year; 'No' if the exact year is known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assessed_state</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Assessed state</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>State of the building at the time of the assessment: original state as built, current state, or after a renovation (with year).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>n_sri_domains_assessed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SRI domains assessed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Number of the 9 SRI technical domains (heating, domestic hot water, cooling, ventilation, lighting, dynamic envelope, electricity, EV charging, monitoring and control) that are present in the building and were assessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sri_domains_not_assessed</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SRI domains not assessed</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domains that are not present in the building and were therefore excluded from the assessment (e.g. no active cooling). These domains do not lower the SRI score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>epc_label</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EPC label</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Energy Performance Certificate label (Norwegian energimerke, A–G) of the building, where known. The EPC rates energy demand and is not directly related to smart readiness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>performance_reference_year</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Performance evaluation reference year</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Year (or last year of the period) to which the building performance values below refer, e.g. the year of the energy measurements, simulation or audit. Needed to compare performance values between buildings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>primary_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Primary energy use intensity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>kWhₚᵣᵢₘ/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Total primary energy use per year, including the energy losses of the supply chain (production, conversion, transmission and delivery), obtained by applying primary energy factors to the delivered energy carriers. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>final_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Final energy use intensity</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Total energy delivered to the building per year (all energy carriers: electricity, district heating, fuels), measured at the building meter or system boundary. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>electricity_use_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Electricity use intensity</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Electricity used by the building per year (all end uses). Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>heating_demand_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Heating energy demand</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Useful (net) energy needed per year to maintain the heating setpoints, before system losses and conversion efficiencies. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cooling_demand_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cooling energy demand</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Useful (net) energy needed per year to maintain the cooling setpoints, before system losses and conversion efficiencies. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dhw_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sanitary hot water energy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Energy used per year to produce sanitary (domestic) hot water. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>lighting_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lighting energy intensity</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Energy used per year by artificial lighting. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hvac_energy_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HVAC energy intensity</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Energy used per year by heating, ventilation and air-conditioning (HVAC): heat and cold generation, fans, pumps and associated equipment. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>peak_heating_load_w_m2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Peak heating load</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>W/m²</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Maximum heating power demand over the year (e.g. highest hourly value). Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>peak_cooling_load_w_m2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Peak cooling load</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>W/m²</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Maximum cooling power demand over the year (e.g. highest hourly value). Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>peak_electricity_load_w_m2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Peak electricity load</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>W/m²</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Maximum electric power demand over the year (e.g. highest hourly value), relevant for grid capacity and energy flexibility. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>peak_final_energy_demand_w_m2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Peak final energy demand</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>W/m²</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Maximum total delivered power demand over the year, all energy carriers combined. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>renewable_generation_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Renewable energy generation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>On-site energy produced per year by renewable sources such as solar PV, solar thermal or wind. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>renewable_self_consumption_pct</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Renewable energy self-consumption</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Share of the on-site renewable generation that is used within the building (not exported), in %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>grid_import_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Grid electricity import</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Electricity imported from the grid per year. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>grid_export_kwh_m2yr</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Grid electricity export</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kWh/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Electricity exported to the grid per year (e.g. surplus PV production). Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>operational_carbon_kgco2e_m2yr</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Operational carbon emissions</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kgCO₂e/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse gas emissions per year caused by the operation of the building (energy use), in CO₂ equivalents. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>embodied_carbon_kgco2e_m2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Embodied carbon</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>kgCO₂e/m²</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse gas emissions from materials and products, construction, replacements and end of life of the building, in CO₂ equivalents (life cycle assessment). Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>whole_life_carbon_kgco2e_m2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Whole-life carbon</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kgCO₂e/m²</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Combined embodied and operational greenhouse gas emissions over the building life cycle, in CO₂ equivalents, for the study period given in 'Whole-life carbon study period'. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>whole_life_carbon_study_period_years</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Whole-life carbon study period</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Length of the study period (reference study period of the life cycle assessment), in years, over which the whole-life carbon is calculated, e.g. 60 years. Needed to compare whole-life carbon values between buildings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>carbon_intensity_energy_kgco2e_kwh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Carbon intensity of energy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>kgCO₂e/kWh</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Average greenhouse gas emissions per kWh of energy used by the building, depending on the energy carriers and their emission factors. Expressed per kWh, not per floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>water_use_m3_m2yr</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Water consumption intensity</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>m³/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Potable water used per year. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>u_value_avg_w_m2k</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Overall heat transfer coefficient (U-value)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>W/(m²·K)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Average thermal transmittance of the building envelope (walls, roof, floor and windows), area-weighted. Lower values mean better insulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>operating_cost_eur_m2yr</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Total operating cost</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>€/(m²·yr)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Annual operating expenses: energy, water, maintenance and other operation costs. Normalized by conditioned (heated/cooled) floor area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>occupant_satisfaction_pct</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Occupant satisfaction</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Building performance</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Occupant satisfaction with the building and its indoor environment, from surveys, normalized to 0–100 % (100 % = fully satisfied).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sri_total_pct</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SRI total score</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SRI</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Total Smart Readiness Indicator (SRI) score, in % of the maximum achievable for this building. It is the weighted combination of the three key functionalities (building, user, grid) and measures how ready the building's technical systems are to use smart technologies. 100 % = fully smart-ready.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sri_class</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SRI class</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SRI</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>SRI class on the official 7-class scale derived from the total score: class 1 = 90–100 %, class 2 = 80–90 %, class 3 = 65–80 %, class 4 = 50–65 %, class 5 = 35–50 %, class 6 = 20–35 %, class 7 = below 20 %.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>latest_renovation_year</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Latest renovation year</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sri_kf1_building_pct</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SRI KF1 – building (energy performance &amp; operation)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SRI key functionality</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Year of the latest major renovation or upgrade of the building and its technical systems, where known.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>SRI key functionality 1 – Energy performance and operation of the building, in %. Combines the impact criteria 'Energy efficiency' and 'Maintenance and fault prediction'.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>reference_year</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Reference year</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sri_kf2_user_pct</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SRI KF2 – response to user needs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SRI key functionality</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Year used to plot buildings against time: the latest renovation year if any, otherwise the construction year. When only a period is known, the middle of the period is used (see 'Reference year estimated').</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>SRI key functionality 2 – Response to user needs, in %. Combines the impact criteria 'Comfort', 'Convenience', 'Health, well-being and accessibility' and 'Information to occupants'.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sri_kf3_grid_pct</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SRI KF3 – energy flexibility (grid)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SRI key functionality</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>SRI key functionality 3 – Energy flexibility, in %: the ability of the building to adapt its energy use to signals from the grid (demand response, load shifting, storage). Equal to the impact criterion 'Energy flexibility and storage'.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>reference_year_estimated</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Reference year estimated</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>'Yes' if the reference year is the midpoint of a construction/renovation period rather than an exact year; 'No' if the exact year is known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>assessed_state</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Assessed state</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>State of the building at the time of the assessment: original state as built, current state, or after a renovation (with year).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>n_sri_domains_assessed</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SRI domains assessed</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sri_impact_energy_efficiency_pct</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SRI impact – Energy efficiency</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SRI impact criteria</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Number of the 9 SRI technical domains (heating, domestic hot water, cooling, ventilation, lighting, dynamic envelope, electricity, EV charging, monitoring and control) that are present in the building and were assessed.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sri_domains_not_assessed</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SRI domains not assessed</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domains that are not present in the building and were therefore excluded from the assessment (e.g. no active cooling). These domains do not lower the SRI score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>epc_label</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>EPC label</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Energy Performance Certificate label (Norwegian energimerke, A–G) of the building, where known. The EPC rates energy demand and is not directly related to smart readiness.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sri_total_pct</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SRI total score</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: energy savings enabled by the smart-ready services (e.g. room-by-room temperature control, demand-controlled ventilation, daylight-dependent lighting).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sri_impact_energy_flexibility_pct</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SRI impact – Energy flexibility and storage</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SRI</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SRI impact criteria</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Total Smart Readiness Indicator (SRI) score, in % of the maximum achievable for this building. It is the weighted combination of the three key functionalities (building, user, grid) and measures how ready the building's technical systems are to use smart technologies. 100 % = fully smart-ready.</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sri_class</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SRI class</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SRI</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>SRI class on the official 7-class scale derived from the total score: class 1 = 90–100 %, class 2 = 80–90 %, class 3 = 65–80 %, class 4 = 50–65 %, class 5 = 35–50 %, class 6 = 20–35 %, class 7 = below 20 %.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sri_kf1_building_pct</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SRI KF1 – building (energy performance &amp; operation)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: ability to shift or reduce energy demand in response to the grid or prices, and to use on-site storage (thermal or electric).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sri_impact_comfort_pct</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SRI impact – Comfort</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SRI key functionality</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SRI impact criteria</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>SRI key functionality 1 – Energy performance and operation of the building, in %. Combines the impact criteria 'Energy efficiency' and 'Maintenance and fault prediction'.</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sri_kf2_user_pct</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SRI KF2 – response to user needs</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: contribution of the smart-ready services to thermal, visual and acoustic comfort of the occupants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sri_impact_convenience_pct</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SRI impact – Convenience</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SRI key functionality</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SRI impact criteria</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>SRI key functionality 2 – Response to user needs, in %. Combines the impact criteria 'Comfort', 'Convenience', 'Health, well-being and accessibility' and 'Information to occupants'.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sri_kf3_grid_pct</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SRI KF3 – energy flexibility (grid)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: how easy the building is to use and operate – automation, fewer manual interventions, user-friendly control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sri_impact_health_wellbeing_pct</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SRI impact – Health, well-being and accessibility</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SRI key functionality</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SRI impact criteria</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>SRI key functionality 3 – Energy flexibility, in %: the ability of the building to adapt its energy use to signals from the grid (demand response, load shifting, storage). Equal to the impact criterion 'Energy flexibility and storage'.</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>sri_impact_energy_efficiency_pct</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>SRI impact – Energy efficiency</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>SRI impact criterion score, in %: contribution to indoor air quality, health, well-being and accessibility for all occupants (including people with reduced mobility).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sri_impact_maintenance_pct</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SRI impact – Maintenance and fault prediction</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>SRI impact criteria</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>SRI impact criterion score, in %: energy savings enabled by the smart-ready services (e.g. room-by-room temperature control, demand-controlled ventilation, daylight-dependent lighting).</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sri_impact_energy_flexibility_pct</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SRI impact – Energy flexibility and storage</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SRI impact criteria</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>SRI impact criterion score, in %: ability to shift or reduce energy demand in response to the grid or prices, and to use on-site storage (thermal or electric).</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>sri_impact_comfort_pct</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SRI impact – Comfort</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SRI impact criteria</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>SRI impact criterion score, in %: contribution of the smart-ready services to thermal, visual and acoustic comfort of the occupants.</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sri_impact_convenience_pct</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SRI impact – Convenience</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SRI impact criteria</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>SRI impact criterion score, in %: how easy the building is to use and operate – automation, fewer manual interventions, user-friendly control.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sri_impact_health_wellbeing_pct</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SRI impact – Health, well-being and accessibility</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SRI impact criteria</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>SRI impact criterion score, in %: contribution to indoor air quality, health, well-being and accessibility for all occupants (including people with reduced mobility).</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sri_impact_maintenance_pct</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>SRI impact – Maintenance and fault prediction</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>SRI impact criteria</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>SRI impact criterion score, in %: automated fault detection and diagnosis, monitoring of equipment status and predictive maintenance of the technical systems.</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sri_impact_information_pct</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SRI impact – Information to occupants</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SRI impact criteria</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>SRI impact criterion score, in %: information given to occupants and facility managers about energy use, indoor conditions and system operation.</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sri_domain_heating_pct</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SRI domain – Heating</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of the heating system – emission control (e.g. room/zone control), heat generation (e.g. heat pump control), distribution, storage and response to grid signals. Can be negative when a service level penalises an impact criterion.</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>sri_domain_dhw_pct</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SRI domain – Domestic hot water</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of the domestic hot water system – control of hot water production and storage, use of renewable sources and response to grid signals. Empty if the domain was not assessed.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>sri_domain_cooling_pct</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SRI domain – Cooling</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of the cooling system – emission and generation control, interlock with heating, flexibility. Empty if the building has no active cooling.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>sri_domain_ventilation_pct</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SRI domain – Ventilation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of the ventilation – demand-controlled air flow, heat recovery control, free cooling and indoor air quality monitoring and feedback.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>sri_domain_lighting_pct</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SRI domain – Lighting</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of artificial lighting – occupancy-based control and daylight-dependent dimming.</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>sri_domain_envelope_pct</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SRI domain – Dynamic building envelope</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of the dynamic building envelope – automated solar shading and window control, and reporting of their status.</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sri_domain_electricity_pct</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SRI domain – Electricity</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of the electricity system – on-site generation (e.g. PV), electricity storage, optimisation of self-consumption, and reporting.</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>sri_domain_ev_charging_pct</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SRI domain – Electric vehicle charging</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of electric vehicle charging – charging capacity, smart / grid-balancing charging and connectivity. Often negative: uncontrolled charging adds peak load and is penalised in the energy flexibility criterion.</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sri_domain_monitoring_control_pct</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SRI domain – Monitoring and control</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SRI technical domains</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>SRI technical domain score, in %: smart readiness of monitoring and control – central building automation, run-time management, fault detection, occupancy detection, reporting and integration with the smart grid.</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>sbp_level</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SbP level</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>level (−2…4)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Overall Smart by Powerhouse (SbP) ambition / maturity level of the building, on the SINTEF tool scale from −2 to 4: −2 No technological equipment, −1 Pre-automated, 0 Automated (today's standard), 1 Smart ready, 2 Smart standard, 3 Smart predictive, 4 Smart cognitive. Decimal values lie between levels.</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>sbp_enabling_technology_level</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SbP level – Enabling technology</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>level (−2…4)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Enabling technology': digital infrastructure such as building automation, sensors, open data standards and interfaces (APIs), BIM / digital twin, connectivity and indoor positioning.</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>sbp_indoor_environment_level</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SbP level – Indoor environment and work environment</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>level (−2…4)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Indoor climate and working environment': thermal comfort, air quality, lighting, acoustics and ergonomics, and how the building adapts them to the users.</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>sbp_energy_resources_level</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SbP level – Energy and resource utilisation</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>level (−2…4)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Energy and resource utilisation': energy efficiency, energy flexibility and interaction with the grid, and efficient use of resources (e.g. waste management).</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>sbp_safety_reliability_level</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SbP level – Safety and reliability</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>level (−2…4)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Safety, security and reliability': physical safety and security (access, fire, flooding and other hazards), cyber security, data privacy and reliable operation.</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>sbp_adaptability_level</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SbP level – Adaptability</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>level (−2…4)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Adaptability': ability of the building, its spaces and its systems to adapt to new uses, users and technologies, and efficient use of floor space.</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>sbp_enabling_technology_pct</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SbP score – Enabling technology</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Enabling technology', in %. The topic level is derived from this percentage.</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>sbp_indoor_environment_pct</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>SbP score – Indoor environment and work environment</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Indoor climate and working environment', in %. The topic level is derived from this percentage.</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>sbp_energy_resources_pct</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SbP score – Energy and resource utilisation</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Energy and resource utilisation', in %. The topic level is derived from this percentage.</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>sbp_safety_reliability_pct</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>SbP score – Safety and reliability</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Safety, security and reliability', in %. The topic level is derived from this percentage.</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>sbp_adaptability_pct</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>SbP score – Adaptability</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Smart by Powerhouse topics</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Adaptability', in %. The topic level is derived from this percentage.</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>assessment_year</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Assessment year</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Metadata</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Year in which the SRI and Smart by Powerhouse assessments of the building were carried out.</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>sri_method</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SRI method / tool</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Metadata</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>SRI calculation method and tool used (e.g. official EC calculation sheet v4.5, U-CERT online tool, or Norway-specific weighting factors). Scores obtained with different methods are not strictly comparable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>sbp_tool</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>SbP tool</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Metadata</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Tool and scale used for the Smart by Powerhouse assessment (SINTEF spreadsheet tool with the −2 to 4 scale, or a modified version).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>detail_available</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Detailed results available</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Metadata</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>'Yes' if detailed results (SRI impact criteria, technical domains, domain × impact matrix and SbP topics) are available for the building; 'No' if only total scores and key functionalities are published.</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>main_reference</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Main information reference</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Main source of the information on this building (short citation). The full reference is listed on the About page.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>main_reference_url</t>
+          <t>sri_impact_information_pct</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Main information reference URL</t>
+          <t>SRI impact – Information to occupants</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>SRI impact criteria</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Web link or DOI of the main information reference, where available.</t>
+          <t>SRI impact criterion score, in %: information given to occupants and facility managers about energy use, indoor conditions and system operation.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>building_info_reference</t>
+          <t>sri_domain_heating_pct</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building information reference</t>
+          <t>SRI domain – Heating</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>SRI technical domains</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Source of the building characteristics: type, size, construction/renovation year and location.</t>
+          <t>SRI technical domain score, in %: smart readiness of the heating system – emission control (e.g. room/zone control), heat generation (e.g. heat pump control), distribution, storage and response to grid signals. Can be negative when a service level penalises an impact criterion.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>building_info_reference_url</t>
+          <t>sri_domain_dhw_pct</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building information reference URL</t>
+          <t>SRI domain – Domestic hot water</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>SRI technical domains</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Web link or DOI of the building information reference, where available.</t>
+          <t>SRI technical domain score, in %: smart readiness of the domestic hot water system – control of hot water production and storage, use of renewable sources and response to grid signals. Empty if the domain was not assessed.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>performance_info_reference</t>
+          <t>sri_domain_cooling_pct</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Performance information reference</t>
+          <t>SRI domain – Cooling</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>SRI technical domains</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Source of the performance results: SRI scores and Smart by Powerhouse levels.</t>
+          <t>SRI technical domain score, in %: smart readiness of the cooling system – emission and generation control, interlock with heating, flexibility. Empty if the building has no active cooling.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>sri_domain_ventilation_pct</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SRI domain – Ventilation</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SRI technical domains</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the ventilation – demand-controlled air flow, heat recovery control, free cooling and indoor air quality monitoring and feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>sri_domain_lighting_pct</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SRI domain – Lighting</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SRI technical domains</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of artificial lighting – occupancy-based control and daylight-dependent dimming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>sri_domain_envelope_pct</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SRI domain – Dynamic building envelope</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SRI technical domains</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the dynamic building envelope – automated solar shading and window control, and reporting of their status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sri_domain_electricity_pct</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SRI domain – Electricity</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SRI technical domains</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of the electricity system – on-site generation (e.g. PV), electricity storage, optimisation of self-consumption, and reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>sri_domain_ev_charging_pct</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SRI domain – Electric vehicle charging</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SRI technical domains</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of electric vehicle charging – charging capacity, smart / grid-balancing charging and connectivity. Often negative: uncontrolled charging adds peak load and is penalised in the energy flexibility criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>sri_domain_monitoring_control_pct</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SRI domain – Monitoring and control</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SRI technical domains</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>SRI technical domain score, in %: smart readiness of monitoring and control – central building automation, run-time management, fault detection, occupancy detection, reporting and integration with the smart grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>sbp_level</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SbP level</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>level (−2…4)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Overall Smart by Powerhouse (SbP) ambition / maturity level of the building, on the SINTEF tool scale from −2 to 4: −2 No technological equipment, −1 Pre-automated, 0 Automated (today's standard), 1 Smart ready, 2 Smart standard, 3 Smart predictive, 4 Smart cognitive. Decimal values lie between levels.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sbp_enabling_technology_level</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SbP level – Enabling technology</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>level (−2…4)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Enabling technology': digital infrastructure such as building automation, sensors, open data standards and interfaces (APIs), BIM / digital twin, connectivity and indoor positioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>sbp_indoor_environment_level</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SbP level – Indoor environment and work environment</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>level (−2…4)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Indoor climate and working environment': thermal comfort, air quality, lighting, acoustics and ergonomics, and how the building adapts them to the users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>sbp_energy_resources_level</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SbP level – Energy and resource utilisation</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>level (−2…4)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Energy and resource utilisation': energy efficiency, energy flexibility and interaction with the grid, and efficient use of resources (e.g. waste management).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>sbp_safety_reliability_level</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SbP level – Safety and reliability</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>level (−2…4)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Safety, security and reliability': physical safety and security (access, fire, flooding and other hazards), cyber security, data privacy and reliable operation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>sbp_adaptability_level</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SbP level – Adaptability</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>level (−2…4)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse level (−2 to 4) for the topic 'Adaptability': ability of the building, its spaces and its systems to adapt to new uses, users and technologies, and efficient use of floor space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sbp_enabling_technology_pct</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SbP score – Enabling technology</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Enabling technology', in %. The topic level is derived from this percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sbp_indoor_environment_pct</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SbP score – Indoor environment and work environment</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Indoor climate and working environment', in %. The topic level is derived from this percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>sbp_energy_resources_pct</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SbP score – Energy and resource utilisation</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Energy and resource utilisation', in %. The topic level is derived from this percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>sbp_safety_reliability_pct</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SbP score – Safety and reliability</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Safety, security and reliability', in %. The topic level is derived from this percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>sbp_adaptability_pct</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SbP score – Adaptability</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Smart by Powerhouse topics</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Share of the available points obtained for the Smart by Powerhouse topic 'Adaptability', in %. The topic level is derived from this percentage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>smartness_assessment_year</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Smartness assessment year</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Year in which the smartness assessment (e.g., SRI or Smart by Powerhouse) of the building was carried out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>sri_method</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SRI method / tool</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>SRI calculation method and tool used (e.g. official EC calculation sheet v4.5, U-CERT online tool, or Norway-specific weighting factors). Scores obtained with different methods are not strictly comparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>sbp_tool</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SbP tool</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Tool and scale used for the Smart by Powerhouse assessment (SINTEF spreadsheet tool with the −2 to 4 scale, or a modified version).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>detail_available</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Detailed results available</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>'Yes' if detailed results (SRI impact criteria, technical domains, domain × impact matrix and SbP topics) are available for the building; 'No' if only total scores and key functionalities are published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>main_reference</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Main information reference</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Main source of the information on this building (short citation). The full reference is listed on the About page.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>main_reference_url</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Main information reference URL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Web link or DOI of the main information reference, where available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>building_info_reference</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Building information reference</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Source of the building characteristics: type, size, construction/renovation year and location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>building_info_reference_url</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Building information reference URL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Web link or DOI of the building information reference, where available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>performance_info_reference</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Performance information reference</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Source of the performance results: SRI scores and Smart by Powerhouse levels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>performance_info_reference_url</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Performance information reference URL</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Web link or DOI of the performance information reference, where available.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Data notes and caveats for this building (inconsistencies in the source, approximations, comparability issues).</t>
         </is>
@@ -15604,9 +15799,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="2" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
